--- a/repaired_template.xlsx
+++ b/repaired_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fujimotogakuto/Library/CloudStorage/GoogleDrive-manamana072554@gmail.com/マイドライブ/営業レポート作成AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24C4836-2C6C-4549-A0D0-5B00B3C6A856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA864DC4-C2CD-A44A-A93C-83B5E0885E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2130,104 +2130,118 @@
       <alignment horizontal="fill" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2237,35 +2251,40 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2279,25 +2298,6 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2598,6 +2598,11 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -2873,6 +2878,11 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -3170,29 +3180,29 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="77"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="153" t="s">
+      <c r="I1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="154"/>
+      <c r="J1" s="80"/>
     </row>
     <row r="2" spans="1:10" ht="13" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="157">
+      <c r="B2" s="87">
         <v>45973</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="75"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="77"/>
       <c r="E2" s="2"/>
       <c r="F2" s="5" t="s">
         <v>4</v>
@@ -3213,11 +3223,11 @@
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="2"/>
       <c r="F3" s="5" t="s">
         <v>9</v>
@@ -3238,11 +3248,11 @@
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="75"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="77"/>
       <c r="E4" s="2"/>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -3263,11 +3273,11 @@
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="74"/>
-      <c r="D5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="77"/>
       <c r="E5" s="2"/>
       <c r="F5" s="14"/>
       <c r="G5" s="15"/>
@@ -3283,11 +3293,11 @@
       <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="77"/>
       <c r="E6" s="2"/>
       <c r="F6" s="5" t="s">
         <v>23</v>
@@ -3308,11 +3318,11 @@
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="77"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5" t="s">
         <v>28</v>
@@ -3333,11 +3343,11 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="124" t="s">
+      <c r="B8" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="74"/>
-      <c r="D8" s="75"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="77"/>
       <c r="E8" s="2"/>
       <c r="F8" s="5"/>
       <c r="G8" s="6"/>
@@ -3353,11 +3363,11 @@
       <c r="A9" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="75"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="77"/>
       <c r="E9" s="2"/>
       <c r="F9" s="5"/>
       <c r="G9" s="6"/>
@@ -3373,12 +3383,12 @@
       <c r="A10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="132">
+      <c r="B10" s="125">
         <f>SUM(B11:D15)/500*100</f>
         <v>45.157771260997059</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="75"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="77"/>
       <c r="E10" s="2"/>
       <c r="F10" s="5"/>
       <c r="G10" s="6"/>
@@ -3394,12 +3404,12 @@
       <c r="A11" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="73">
+      <c r="B11" s="152">
         <f>H2</f>
         <v>0</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="77"/>
       <c r="E11" s="2"/>
       <c r="F11" s="3"/>
       <c r="G11" s="6"/>
@@ -3411,12 +3421,12 @@
       <c r="A12" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="91">
+      <c r="B12" s="108">
         <f>H3</f>
         <v>77.272727272727266</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77"/>
       <c r="E12" s="2"/>
       <c r="F12" s="21"/>
       <c r="G12" s="6"/>
@@ -3428,12 +3438,12 @@
       <c r="A13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="91">
+      <c r="B13" s="108">
         <f>H4</f>
         <v>84</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="75"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="77"/>
       <c r="E13" s="6"/>
       <c r="F13" s="14"/>
       <c r="G13" s="15"/>
@@ -3445,12 +3455,12 @@
       <c r="A14" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="91">
+      <c r="B14" s="108">
         <f>H6</f>
         <v>64.516129032258064</v>
       </c>
-      <c r="C14" s="74"/>
-      <c r="D14" s="75"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="77"/>
       <c r="E14" s="6"/>
       <c r="F14" s="14"/>
       <c r="G14" s="15"/>
@@ -3462,12 +3472,12 @@
       <c r="A15" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="148">
+      <c r="B15" s="155">
         <f>H7</f>
         <v>0</v>
       </c>
-      <c r="C15" s="149"/>
-      <c r="D15" s="150"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="157"/>
       <c r="E15" s="6"/>
       <c r="F15" s="14"/>
       <c r="G15" s="15"/>
@@ -3476,12 +3486,12 @@
       <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:10" ht="13" customHeight="1">
-      <c r="A16" s="102" t="s">
+      <c r="A16" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="75"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="77"/>
       <c r="E16" s="25"/>
       <c r="F16" s="14"/>
       <c r="G16" s="26"/>
@@ -3490,10 +3500,10 @@
       <c r="J16" s="27"/>
     </row>
     <row r="17" spans="1:10" ht="14" customHeight="1">
-      <c r="A17" s="137"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="139"/>
+      <c r="A17" s="119"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="121"/>
       <c r="E17" s="28"/>
       <c r="F17" s="14"/>
       <c r="G17" s="26"/>
@@ -3506,10 +3516,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="135"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="140"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="122"/>
       <c r="E18" s="28"/>
       <c r="F18" s="14"/>
       <c r="G18" s="26"/>
@@ -3522,10 +3532,10 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A19" s="97"/>
-      <c r="B19" s="135"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="140"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="122"/>
       <c r="E19" s="28"/>
       <c r="F19" s="14" t="s">
         <v>51</v>
@@ -3540,10 +3550,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A20" s="97"/>
-      <c r="B20" s="135"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="140"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="122"/>
       <c r="E20" s="28"/>
       <c r="F20" s="14" t="s">
         <v>54</v>
@@ -3557,10 +3567,10 @@
       <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="13" customHeight="1">
-      <c r="A21" s="97"/>
-      <c r="B21" s="135"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="140"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="122"/>
       <c r="E21" s="28"/>
       <c r="F21" s="14" t="s">
         <v>55</v>
@@ -3574,10 +3584,10 @@
       <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="13" customHeight="1">
-      <c r="A22" s="97"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="140"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="122"/>
       <c r="E22" s="28"/>
       <c r="F22" s="14" t="s">
         <v>56</v>
@@ -3591,10 +3601,10 @@
       <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="13" customHeight="1">
-      <c r="A23" s="97"/>
-      <c r="B23" s="135"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="140"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="122"/>
       <c r="E23" s="28"/>
       <c r="F23" s="14" t="s">
         <v>57</v>
@@ -3608,10 +3618,10 @@
       <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="13" customHeight="1">
-      <c r="A24" s="97"/>
-      <c r="B24" s="135"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="140"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="122"/>
       <c r="E24" s="28"/>
       <c r="F24" s="14" t="s">
         <v>58</v>
@@ -3622,10 +3632,10 @@
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" ht="13" customHeight="1">
-      <c r="A25" s="97"/>
-      <c r="B25" s="135"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="140"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="122"/>
       <c r="E25" s="28"/>
       <c r="F25" s="14"/>
       <c r="G25" s="26"/>
@@ -3636,10 +3646,10 @@
       <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" ht="13" customHeight="1">
-      <c r="A26" s="97"/>
-      <c r="B26" s="135"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="140"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="122"/>
       <c r="E26" s="25"/>
       <c r="F26" s="14"/>
       <c r="G26" s="26"/>
@@ -3650,10 +3660,10 @@
       <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10" ht="13" customHeight="1">
-      <c r="A27" s="97"/>
-      <c r="B27" s="135"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="140"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="122"/>
       <c r="E27" s="25"/>
       <c r="F27" s="14"/>
       <c r="G27" s="26"/>
@@ -3664,10 +3674,10 @@
       <c r="J27" s="13"/>
     </row>
     <row r="28" spans="1:10" ht="13" customHeight="1">
-      <c r="A28" s="97"/>
-      <c r="B28" s="135"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="140"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="113"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="122"/>
       <c r="E28" s="25"/>
       <c r="F28" s="14"/>
       <c r="G28" s="26"/>
@@ -3678,10 +3688,10 @@
       <c r="J28" s="13"/>
     </row>
     <row r="29" spans="1:10" ht="13" customHeight="1">
-      <c r="A29" s="97"/>
-      <c r="B29" s="135"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="140"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="113"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="122"/>
       <c r="E29" s="25"/>
       <c r="F29" s="14"/>
       <c r="G29" s="26"/>
@@ -3690,10 +3700,10 @@
       <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:10" ht="13" customHeight="1">
-      <c r="A30" s="97"/>
-      <c r="B30" s="135"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="140"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="122"/>
       <c r="E30" s="25"/>
       <c r="F30" s="14"/>
       <c r="G30" s="26"/>
@@ -3702,10 +3712,10 @@
       <c r="J30" s="13"/>
     </row>
     <row r="31" spans="1:10" ht="13" customHeight="1">
-      <c r="A31" s="141"/>
-      <c r="B31" s="112"/>
-      <c r="C31" s="112"/>
-      <c r="D31" s="113"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="123"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="124"/>
       <c r="E31" s="25"/>
       <c r="F31" s="14"/>
       <c r="G31" s="26"/>
@@ -3725,304 +3735,304 @@
       <c r="I32" s="15"/>
     </row>
     <row r="33" spans="1:10" ht="23" customHeight="1">
-      <c r="A33" s="93" t="s">
+      <c r="A33" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="95"/>
-      <c r="F33" s="93" t="s">
+      <c r="B33" s="97"/>
+      <c r="C33" s="97"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="95"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="98"/>
     </row>
     <row r="34" spans="1:10" ht="13" customHeight="1">
-      <c r="A34" s="99" t="s">
+      <c r="A34" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="100"/>
-      <c r="C34" s="103" t="s">
+      <c r="B34" s="150"/>
+      <c r="C34" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="104"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="125" t="s">
+      <c r="D34" s="141"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="126"/>
-      <c r="H34" s="142" t="s">
+      <c r="G34" s="134"/>
+      <c r="H34" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="I34" s="143"/>
-      <c r="J34" s="144"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="105"/>
     </row>
     <row r="35" spans="1:10" ht="13" customHeight="1">
-      <c r="A35" s="106" t="s">
+      <c r="A35" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="107"/>
-      <c r="C35" s="114" t="s">
+      <c r="B35" s="89"/>
+      <c r="C35" s="145" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="115"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="106" t="s">
+      <c r="D35" s="146"/>
+      <c r="E35" s="144"/>
+      <c r="F35" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="107"/>
+      <c r="G35" s="89"/>
       <c r="H35" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="I35" s="109" t="s">
+      <c r="I35" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="J35" s="110"/>
+      <c r="J35" s="144"/>
     </row>
     <row r="36" spans="1:10" ht="13" customHeight="1">
-      <c r="A36" s="89" t="s">
+      <c r="A36" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="90"/>
-      <c r="C36" s="77" t="s">
+      <c r="B36" s="83"/>
+      <c r="C36" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="78"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="89" t="s">
+      <c r="D36" s="86"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="G36" s="90"/>
+      <c r="G36" s="83"/>
       <c r="H36" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="I36" s="98" t="s">
+      <c r="I36" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J36" s="79"/>
+      <c r="J36" s="74"/>
     </row>
     <row r="37" spans="1:10" ht="13" customHeight="1">
-      <c r="A37" s="89" t="s">
+      <c r="A37" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="90"/>
-      <c r="C37" s="77" t="s">
+      <c r="B37" s="83"/>
+      <c r="C37" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="78"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="89" t="s">
+      <c r="D37" s="86"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="90"/>
+      <c r="G37" s="83"/>
       <c r="H37" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I37" s="98" t="s">
+      <c r="I37" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="J37" s="79"/>
+      <c r="J37" s="74"/>
     </row>
     <row r="38" spans="1:10" ht="13" customHeight="1">
-      <c r="A38" s="89" t="s">
+      <c r="A38" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="90"/>
-      <c r="C38" s="77" t="s">
+      <c r="B38" s="83"/>
+      <c r="C38" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="89" t="s">
+      <c r="D38" s="86"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="G38" s="90"/>
+      <c r="G38" s="83"/>
       <c r="H38" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="98" t="s">
+      <c r="I38" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="J38" s="79"/>
+      <c r="J38" s="74"/>
     </row>
     <row r="39" spans="1:10" ht="13" customHeight="1">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="77" t="s">
+      <c r="B39" s="83"/>
+      <c r="C39" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="78"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="89" t="s">
+      <c r="D39" s="86"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="G39" s="90"/>
+      <c r="G39" s="83"/>
       <c r="H39" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="I39" s="98" t="s">
+      <c r="I39" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="J39" s="79"/>
+      <c r="J39" s="74"/>
     </row>
     <row r="40" spans="1:10" ht="13" customHeight="1">
-      <c r="A40" s="89" t="s">
+      <c r="A40" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="90"/>
-      <c r="C40" s="77" t="s">
+      <c r="B40" s="83"/>
+      <c r="C40" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="D40" s="78"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="89" t="s">
+      <c r="D40" s="86"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="G40" s="90"/>
+      <c r="G40" s="83"/>
       <c r="H40" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="I40" s="98" t="s">
+      <c r="I40" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="J40" s="79"/>
+      <c r="J40" s="74"/>
     </row>
     <row r="41" spans="1:10" ht="13" customHeight="1">
-      <c r="A41" s="89" t="s">
+      <c r="A41" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="90"/>
-      <c r="C41" s="77" t="s">
+      <c r="B41" s="83"/>
+      <c r="C41" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="78"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="89" t="s">
+      <c r="D41" s="86"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="G41" s="90"/>
+      <c r="G41" s="83"/>
       <c r="H41" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I41" s="98" t="s">
+      <c r="I41" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="J41" s="79"/>
+      <c r="J41" s="74"/>
     </row>
     <row r="42" spans="1:10" ht="13" customHeight="1">
-      <c r="A42" s="89" t="s">
+      <c r="A42" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="90"/>
-      <c r="C42" s="77" t="s">
+      <c r="B42" s="83"/>
+      <c r="C42" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="78"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="89" t="s">
+      <c r="D42" s="86"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="G42" s="90"/>
+      <c r="G42" s="83"/>
       <c r="H42" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="I42" s="98" t="s">
+      <c r="I42" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="J42" s="79"/>
+      <c r="J42" s="74"/>
     </row>
     <row r="43" spans="1:10" ht="13" customHeight="1">
-      <c r="A43" s="89" t="s">
+      <c r="A43" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="90"/>
-      <c r="C43" s="77" t="s">
+      <c r="B43" s="83"/>
+      <c r="C43" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="78"/>
-      <c r="E43" s="79"/>
-      <c r="F43" s="89" t="s">
+      <c r="D43" s="86"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="G43" s="90"/>
+      <c r="G43" s="83"/>
       <c r="H43" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="I43" s="98" t="s">
+      <c r="I43" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="J43" s="79"/>
+      <c r="J43" s="74"/>
     </row>
     <row r="44" spans="1:10" ht="13" customHeight="1">
-      <c r="A44" s="89" t="s">
+      <c r="A44" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="B44" s="90"/>
-      <c r="C44" s="77" t="s">
+      <c r="B44" s="83"/>
+      <c r="C44" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="78"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="89" t="s">
+      <c r="D44" s="86"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="G44" s="90"/>
+      <c r="G44" s="83"/>
       <c r="H44" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="I44" s="98" t="s">
+      <c r="I44" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="J44" s="79"/>
+      <c r="J44" s="74"/>
     </row>
     <row r="45" spans="1:10" ht="13" customHeight="1">
-      <c r="A45" s="89" t="s">
+      <c r="A45" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="B45" s="90"/>
-      <c r="C45" s="77" t="s">
+      <c r="B45" s="83"/>
+      <c r="C45" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="78"/>
-      <c r="E45" s="79"/>
-      <c r="F45" s="89" t="s">
+      <c r="D45" s="86"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="G45" s="90"/>
+      <c r="G45" s="83"/>
       <c r="H45" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="I45" s="98" t="s">
+      <c r="I45" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="J45" s="79"/>
+      <c r="J45" s="74"/>
     </row>
     <row r="46" spans="1:10" ht="13" customHeight="1">
-      <c r="A46" s="130" t="s">
+      <c r="A46" s="126" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="131"/>
-      <c r="C46" s="127" t="s">
+      <c r="B46" s="127"/>
+      <c r="C46" s="135" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="128"/>
-      <c r="E46" s="123"/>
-      <c r="F46" s="130" t="s">
+      <c r="D46" s="136"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="126" t="s">
         <v>96</v>
       </c>
-      <c r="G46" s="131"/>
+      <c r="G46" s="127"/>
       <c r="H46" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="I46" s="122" t="s">
+      <c r="I46" s="131" t="s">
         <v>98</v>
       </c>
-      <c r="J46" s="123"/>
+      <c r="J46" s="132"/>
     </row>
     <row r="47" spans="1:10" ht="13" customHeight="1">
       <c r="A47" s="37"/>
@@ -4036,260 +4046,260 @@
       <c r="I47" s="42"/>
     </row>
     <row r="48" spans="1:10" ht="13" customHeight="1">
-      <c r="A48" s="116" t="s">
+      <c r="A48" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="117"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="117"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="117"/>
-      <c r="H48" s="117"/>
-      <c r="I48" s="117"/>
-      <c r="J48" s="118"/>
+      <c r="B48" s="110"/>
+      <c r="C48" s="110"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="110"/>
+      <c r="F48" s="110"/>
+      <c r="G48" s="110"/>
+      <c r="H48" s="110"/>
+      <c r="I48" s="110"/>
+      <c r="J48" s="111"/>
     </row>
     <row r="49" spans="1:10" ht="13" customHeight="1">
-      <c r="A49" s="119"/>
-      <c r="B49" s="120"/>
-      <c r="C49" s="120"/>
-      <c r="D49" s="120"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="120"/>
-      <c r="J49" s="121"/>
+      <c r="A49" s="115"/>
+      <c r="B49" s="116"/>
+      <c r="C49" s="116"/>
+      <c r="D49" s="116"/>
+      <c r="E49" s="116"/>
+      <c r="F49" s="116"/>
+      <c r="G49" s="116"/>
+      <c r="H49" s="116"/>
+      <c r="I49" s="116"/>
+      <c r="J49" s="117"/>
     </row>
     <row r="50" spans="1:10" ht="12" customHeight="1">
-      <c r="A50" s="133" t="s">
+      <c r="A50" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="117"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="117"/>
-      <c r="J50" s="118"/>
+      <c r="B50" s="110"/>
+      <c r="C50" s="110"/>
+      <c r="D50" s="110"/>
+      <c r="E50" s="110"/>
+      <c r="F50" s="110"/>
+      <c r="G50" s="110"/>
+      <c r="H50" s="110"/>
+      <c r="I50" s="110"/>
+      <c r="J50" s="111"/>
     </row>
     <row r="51" spans="1:10" ht="12" customHeight="1">
-      <c r="A51" s="134"/>
-      <c r="B51" s="135"/>
-      <c r="C51" s="135"/>
-      <c r="D51" s="135"/>
-      <c r="E51" s="135"/>
-      <c r="F51" s="135"/>
-      <c r="G51" s="135"/>
-      <c r="H51" s="135"/>
-      <c r="I51" s="135"/>
-      <c r="J51" s="136"/>
+      <c r="A51" s="112"/>
+      <c r="B51" s="113"/>
+      <c r="C51" s="113"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="113"/>
+      <c r="F51" s="113"/>
+      <c r="G51" s="113"/>
+      <c r="H51" s="113"/>
+      <c r="I51" s="113"/>
+      <c r="J51" s="114"/>
     </row>
     <row r="52" spans="1:10" ht="12" customHeight="1">
-      <c r="A52" s="134"/>
-      <c r="B52" s="135"/>
-      <c r="C52" s="135"/>
-      <c r="D52" s="135"/>
-      <c r="E52" s="135"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
-      <c r="H52" s="135"/>
-      <c r="I52" s="135"/>
-      <c r="J52" s="136"/>
+      <c r="A52" s="112"/>
+      <c r="B52" s="113"/>
+      <c r="C52" s="113"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="113"/>
+      <c r="F52" s="113"/>
+      <c r="G52" s="113"/>
+      <c r="H52" s="113"/>
+      <c r="I52" s="113"/>
+      <c r="J52" s="114"/>
     </row>
     <row r="53" spans="1:10" ht="12" customHeight="1">
-      <c r="A53" s="134"/>
-      <c r="B53" s="135"/>
-      <c r="C53" s="135"/>
-      <c r="D53" s="135"/>
-      <c r="E53" s="135"/>
-      <c r="F53" s="135"/>
-      <c r="G53" s="135"/>
-      <c r="H53" s="135"/>
-      <c r="I53" s="135"/>
-      <c r="J53" s="136"/>
+      <c r="A53" s="112"/>
+      <c r="B53" s="113"/>
+      <c r="C53" s="113"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="113"/>
+      <c r="F53" s="113"/>
+      <c r="G53" s="113"/>
+      <c r="H53" s="113"/>
+      <c r="I53" s="113"/>
+      <c r="J53" s="114"/>
     </row>
     <row r="54" spans="1:10" ht="12" customHeight="1">
-      <c r="A54" s="134"/>
-      <c r="B54" s="135"/>
-      <c r="C54" s="135"/>
-      <c r="D54" s="135"/>
-      <c r="E54" s="135"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="135"/>
-      <c r="H54" s="135"/>
-      <c r="I54" s="135"/>
-      <c r="J54" s="136"/>
+      <c r="A54" s="112"/>
+      <c r="B54" s="113"/>
+      <c r="C54" s="113"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="113"/>
+      <c r="F54" s="113"/>
+      <c r="G54" s="113"/>
+      <c r="H54" s="113"/>
+      <c r="I54" s="113"/>
+      <c r="J54" s="114"/>
     </row>
     <row r="55" spans="1:10" ht="12" customHeight="1">
-      <c r="A55" s="134"/>
-      <c r="B55" s="135"/>
-      <c r="C55" s="135"/>
-      <c r="D55" s="135"/>
-      <c r="E55" s="135"/>
-      <c r="F55" s="135"/>
-      <c r="G55" s="135"/>
-      <c r="H55" s="135"/>
-      <c r="I55" s="135"/>
-      <c r="J55" s="136"/>
+      <c r="A55" s="112"/>
+      <c r="B55" s="113"/>
+      <c r="C55" s="113"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="113"/>
+      <c r="F55" s="113"/>
+      <c r="G55" s="113"/>
+      <c r="H55" s="113"/>
+      <c r="I55" s="113"/>
+      <c r="J55" s="114"/>
     </row>
     <row r="56" spans="1:10" ht="12" customHeight="1">
-      <c r="A56" s="134"/>
-      <c r="B56" s="135"/>
-      <c r="C56" s="135"/>
-      <c r="D56" s="135"/>
-      <c r="E56" s="135"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="135"/>
-      <c r="H56" s="135"/>
-      <c r="I56" s="135"/>
-      <c r="J56" s="136"/>
+      <c r="A56" s="112"/>
+      <c r="B56" s="113"/>
+      <c r="C56" s="113"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="113"/>
+      <c r="G56" s="113"/>
+      <c r="H56" s="113"/>
+      <c r="I56" s="113"/>
+      <c r="J56" s="114"/>
     </row>
     <row r="57" spans="1:10" ht="12" customHeight="1">
-      <c r="A57" s="134"/>
-      <c r="B57" s="135"/>
-      <c r="C57" s="135"/>
-      <c r="D57" s="135"/>
-      <c r="E57" s="135"/>
-      <c r="F57" s="135"/>
-      <c r="G57" s="135"/>
-      <c r="H57" s="135"/>
-      <c r="I57" s="135"/>
-      <c r="J57" s="136"/>
+      <c r="A57" s="112"/>
+      <c r="B57" s="113"/>
+      <c r="C57" s="113"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="113"/>
+      <c r="G57" s="113"/>
+      <c r="H57" s="113"/>
+      <c r="I57" s="113"/>
+      <c r="J57" s="114"/>
     </row>
     <row r="58" spans="1:10" ht="12" customHeight="1">
-      <c r="A58" s="134"/>
-      <c r="B58" s="135"/>
-      <c r="C58" s="135"/>
-      <c r="D58" s="135"/>
-      <c r="E58" s="135"/>
-      <c r="F58" s="135"/>
-      <c r="G58" s="135"/>
-      <c r="H58" s="135"/>
-      <c r="I58" s="135"/>
-      <c r="J58" s="136"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="113"/>
+      <c r="C58" s="113"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="113"/>
+      <c r="F58" s="113"/>
+      <c r="G58" s="113"/>
+      <c r="H58" s="113"/>
+      <c r="I58" s="113"/>
+      <c r="J58" s="114"/>
     </row>
     <row r="59" spans="1:10" ht="12" customHeight="1">
-      <c r="A59" s="134"/>
-      <c r="B59" s="135"/>
-      <c r="C59" s="135"/>
-      <c r="D59" s="135"/>
-      <c r="E59" s="135"/>
-      <c r="F59" s="135"/>
-      <c r="G59" s="135"/>
-      <c r="H59" s="135"/>
-      <c r="I59" s="135"/>
-      <c r="J59" s="136"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="113"/>
+      <c r="C59" s="113"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="113"/>
+      <c r="F59" s="113"/>
+      <c r="G59" s="113"/>
+      <c r="H59" s="113"/>
+      <c r="I59" s="113"/>
+      <c r="J59" s="114"/>
     </row>
     <row r="60" spans="1:10" ht="12" customHeight="1">
-      <c r="A60" s="134"/>
-      <c r="B60" s="135"/>
-      <c r="C60" s="135"/>
-      <c r="D60" s="135"/>
-      <c r="E60" s="135"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="135"/>
-      <c r="H60" s="135"/>
-      <c r="I60" s="135"/>
-      <c r="J60" s="136"/>
+      <c r="A60" s="112"/>
+      <c r="B60" s="113"/>
+      <c r="C60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="114"/>
     </row>
     <row r="61" spans="1:10" ht="12" customHeight="1">
-      <c r="A61" s="134"/>
-      <c r="B61" s="135"/>
-      <c r="C61" s="135"/>
-      <c r="D61" s="135"/>
-      <c r="E61" s="135"/>
-      <c r="F61" s="135"/>
-      <c r="G61" s="135"/>
-      <c r="H61" s="135"/>
-      <c r="I61" s="135"/>
-      <c r="J61" s="136"/>
+      <c r="A61" s="112"/>
+      <c r="B61" s="113"/>
+      <c r="C61" s="113"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="113"/>
+      <c r="G61" s="113"/>
+      <c r="H61" s="113"/>
+      <c r="I61" s="113"/>
+      <c r="J61" s="114"/>
     </row>
     <row r="62" spans="1:10" ht="12" customHeight="1">
-      <c r="A62" s="134"/>
-      <c r="B62" s="135"/>
-      <c r="C62" s="135"/>
-      <c r="D62" s="135"/>
-      <c r="E62" s="135"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="135"/>
-      <c r="H62" s="135"/>
-      <c r="I62" s="135"/>
-      <c r="J62" s="136"/>
+      <c r="A62" s="112"/>
+      <c r="B62" s="113"/>
+      <c r="C62" s="113"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="113"/>
+      <c r="H62" s="113"/>
+      <c r="I62" s="113"/>
+      <c r="J62" s="114"/>
     </row>
     <row r="63" spans="1:10" ht="12" customHeight="1">
-      <c r="A63" s="134"/>
-      <c r="B63" s="135"/>
-      <c r="C63" s="135"/>
-      <c r="D63" s="135"/>
-      <c r="E63" s="135"/>
-      <c r="F63" s="135"/>
-      <c r="G63" s="135"/>
-      <c r="H63" s="135"/>
-      <c r="I63" s="135"/>
-      <c r="J63" s="136"/>
+      <c r="A63" s="112"/>
+      <c r="B63" s="113"/>
+      <c r="C63" s="113"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="113"/>
+      <c r="F63" s="113"/>
+      <c r="G63" s="113"/>
+      <c r="H63" s="113"/>
+      <c r="I63" s="113"/>
+      <c r="J63" s="114"/>
     </row>
     <row r="64" spans="1:10" ht="12" customHeight="1">
-      <c r="A64" s="134"/>
-      <c r="B64" s="135"/>
-      <c r="C64" s="135"/>
-      <c r="D64" s="135"/>
-      <c r="E64" s="135"/>
-      <c r="F64" s="135"/>
-      <c r="G64" s="135"/>
-      <c r="H64" s="135"/>
-      <c r="I64" s="135"/>
-      <c r="J64" s="136"/>
+      <c r="A64" s="112"/>
+      <c r="B64" s="113"/>
+      <c r="C64" s="113"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="113"/>
+      <c r="G64" s="113"/>
+      <c r="H64" s="113"/>
+      <c r="I64" s="113"/>
+      <c r="J64" s="114"/>
     </row>
     <row r="65" spans="1:10" ht="12" customHeight="1">
-      <c r="A65" s="134"/>
-      <c r="B65" s="135"/>
-      <c r="C65" s="135"/>
-      <c r="D65" s="135"/>
-      <c r="E65" s="135"/>
-      <c r="F65" s="135"/>
-      <c r="G65" s="135"/>
-      <c r="H65" s="135"/>
-      <c r="I65" s="135"/>
-      <c r="J65" s="136"/>
+      <c r="A65" s="112"/>
+      <c r="B65" s="113"/>
+      <c r="C65" s="113"/>
+      <c r="D65" s="113"/>
+      <c r="E65" s="113"/>
+      <c r="F65" s="113"/>
+      <c r="G65" s="113"/>
+      <c r="H65" s="113"/>
+      <c r="I65" s="113"/>
+      <c r="J65" s="114"/>
     </row>
     <row r="66" spans="1:10" ht="12" customHeight="1">
-      <c r="A66" s="134"/>
-      <c r="B66" s="135"/>
-      <c r="C66" s="135"/>
-      <c r="D66" s="135"/>
-      <c r="E66" s="135"/>
-      <c r="F66" s="135"/>
-      <c r="G66" s="135"/>
-      <c r="H66" s="135"/>
-      <c r="I66" s="135"/>
-      <c r="J66" s="136"/>
+      <c r="A66" s="112"/>
+      <c r="B66" s="113"/>
+      <c r="C66" s="113"/>
+      <c r="D66" s="113"/>
+      <c r="E66" s="113"/>
+      <c r="F66" s="113"/>
+      <c r="G66" s="113"/>
+      <c r="H66" s="113"/>
+      <c r="I66" s="113"/>
+      <c r="J66" s="114"/>
     </row>
     <row r="67" spans="1:10" ht="12" customHeight="1">
-      <c r="A67" s="134"/>
-      <c r="B67" s="135"/>
-      <c r="C67" s="135"/>
-      <c r="D67" s="135"/>
-      <c r="E67" s="135"/>
-      <c r="F67" s="135"/>
-      <c r="G67" s="135"/>
-      <c r="H67" s="135"/>
-      <c r="I67" s="135"/>
-      <c r="J67" s="136"/>
+      <c r="A67" s="112"/>
+      <c r="B67" s="113"/>
+      <c r="C67" s="113"/>
+      <c r="D67" s="113"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="113"/>
+      <c r="G67" s="113"/>
+      <c r="H67" s="113"/>
+      <c r="I67" s="113"/>
+      <c r="J67" s="114"/>
     </row>
     <row r="68" spans="1:10" ht="12" customHeight="1">
-      <c r="A68" s="119"/>
-      <c r="B68" s="120"/>
-      <c r="C68" s="120"/>
-      <c r="D68" s="120"/>
-      <c r="E68" s="120"/>
-      <c r="F68" s="120"/>
-      <c r="G68" s="120"/>
-      <c r="H68" s="120"/>
-      <c r="I68" s="120"/>
-      <c r="J68" s="121"/>
+      <c r="A68" s="115"/>
+      <c r="B68" s="116"/>
+      <c r="C68" s="116"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="116"/>
+      <c r="F68" s="116"/>
+      <c r="G68" s="116"/>
+      <c r="H68" s="116"/>
+      <c r="I68" s="116"/>
+      <c r="J68" s="117"/>
     </row>
     <row r="69" spans="1:10" ht="13" customHeight="1">
       <c r="A69" s="42"/>
@@ -4313,11 +4323,11 @@
       <c r="C70" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="D70" s="146" t="s">
+      <c r="D70" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="E70" s="74"/>
-      <c r="F70" s="75"/>
+      <c r="E70" s="76"/>
+      <c r="F70" s="77"/>
       <c r="G70" s="45" t="s">
         <v>103</v>
       </c>
@@ -4332,34 +4342,34 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="22" customHeight="1">
-      <c r="A71" s="111" t="s">
+      <c r="A71" s="128" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="112"/>
-      <c r="C71" s="112"/>
-      <c r="D71" s="112"/>
-      <c r="E71" s="112"/>
-      <c r="F71" s="112"/>
-      <c r="G71" s="112"/>
-      <c r="H71" s="112"/>
-      <c r="I71" s="112"/>
-      <c r="J71" s="113"/>
+      <c r="B71" s="123"/>
+      <c r="C71" s="123"/>
+      <c r="D71" s="123"/>
+      <c r="E71" s="123"/>
+      <c r="F71" s="123"/>
+      <c r="G71" s="123"/>
+      <c r="H71" s="123"/>
+      <c r="I71" s="123"/>
+      <c r="J71" s="124"/>
     </row>
     <row r="72" spans="1:10" ht="14" customHeight="1">
-      <c r="A72" s="145" t="s">
+      <c r="A72" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="B72" s="80" t="s">
+      <c r="B72" s="148" t="s">
         <v>109</v>
       </c>
       <c r="C72" s="47">
         <v>1</v>
       </c>
-      <c r="D72" s="76" t="s">
+      <c r="D72" s="81" t="s">
         <v>110</v>
       </c>
-      <c r="E72" s="74"/>
-      <c r="F72" s="75"/>
+      <c r="E72" s="76"/>
+      <c r="F72" s="77"/>
       <c r="G72" s="48"/>
       <c r="H72" s="49">
         <f t="shared" ref="H72:H81" si="0">IF(G72="〇", 1, IF(G72="△", 0.5, 0))</f>
@@ -4373,16 +4383,16 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="14" customHeight="1">
-      <c r="A73" s="81"/>
-      <c r="B73" s="81"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="94"/>
       <c r="C73" s="47">
         <v>2</v>
       </c>
-      <c r="D73" s="76" t="s">
+      <c r="D73" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="E73" s="74"/>
-      <c r="F73" s="75"/>
+      <c r="E73" s="76"/>
+      <c r="F73" s="77"/>
       <c r="G73" s="48"/>
       <c r="H73" s="49">
         <f t="shared" si="0"/>
@@ -4396,16 +4406,16 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="14" customHeight="1">
-      <c r="A74" s="81"/>
-      <c r="B74" s="82"/>
+      <c r="A74" s="94"/>
+      <c r="B74" s="95"/>
       <c r="C74" s="47">
         <v>3</v>
       </c>
-      <c r="D74" s="76" t="s">
+      <c r="D74" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="E74" s="74"/>
-      <c r="F74" s="75"/>
+      <c r="E74" s="76"/>
+      <c r="F74" s="77"/>
       <c r="G74" s="48"/>
       <c r="H74" s="49">
         <f t="shared" si="0"/>
@@ -4419,18 +4429,18 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="13" customHeight="1">
-      <c r="A75" s="81"/>
-      <c r="B75" s="80" t="s">
+      <c r="A75" s="94"/>
+      <c r="B75" s="148" t="s">
         <v>117</v>
       </c>
       <c r="C75" s="47">
         <v>4</v>
       </c>
-      <c r="D75" s="76" t="s">
+      <c r="D75" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="E75" s="74"/>
-      <c r="F75" s="75"/>
+      <c r="E75" s="76"/>
+      <c r="F75" s="77"/>
       <c r="G75" s="48"/>
       <c r="H75" s="49">
         <f t="shared" si="0"/>
@@ -4442,16 +4452,16 @@
       <c r="J75" s="52"/>
     </row>
     <row r="76" spans="1:10" ht="14" customHeight="1">
-      <c r="A76" s="81"/>
-      <c r="B76" s="81"/>
+      <c r="A76" s="94"/>
+      <c r="B76" s="94"/>
       <c r="C76" s="47">
         <v>5</v>
       </c>
-      <c r="D76" s="76" t="s">
+      <c r="D76" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="E76" s="74"/>
-      <c r="F76" s="75"/>
+      <c r="E76" s="76"/>
+      <c r="F76" s="77"/>
       <c r="G76" s="48"/>
       <c r="H76" s="49">
         <f t="shared" si="0"/>
@@ -4465,16 +4475,16 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="13" customHeight="1">
-      <c r="A77" s="81"/>
-      <c r="B77" s="81"/>
+      <c r="A77" s="94"/>
+      <c r="B77" s="94"/>
       <c r="C77" s="47">
         <v>6</v>
       </c>
-      <c r="D77" s="76" t="s">
+      <c r="D77" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="E77" s="74"/>
-      <c r="F77" s="75"/>
+      <c r="E77" s="76"/>
+      <c r="F77" s="77"/>
       <c r="G77" s="48"/>
       <c r="H77" s="49">
         <f t="shared" si="0"/>
@@ -4486,16 +4496,16 @@
       <c r="J77" s="51"/>
     </row>
     <row r="78" spans="1:10" ht="14" customHeight="1">
-      <c r="A78" s="81"/>
-      <c r="B78" s="82"/>
+      <c r="A78" s="94"/>
+      <c r="B78" s="95"/>
       <c r="C78" s="47">
         <v>7</v>
       </c>
-      <c r="D78" s="76" t="s">
+      <c r="D78" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="E78" s="74"/>
-      <c r="F78" s="75"/>
+      <c r="E78" s="76"/>
+      <c r="F78" s="77"/>
       <c r="G78" s="48"/>
       <c r="H78" s="49">
         <f t="shared" si="0"/>
@@ -4509,18 +4519,18 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="13" customHeight="1">
-      <c r="A79" s="81"/>
-      <c r="B79" s="147" t="s">
+      <c r="A79" s="94"/>
+      <c r="B79" s="154" t="s">
         <v>128</v>
       </c>
       <c r="C79" s="53">
         <v>8</v>
       </c>
-      <c r="D79" s="76" t="s">
+      <c r="D79" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="E79" s="74"/>
-      <c r="F79" s="75"/>
+      <c r="E79" s="76"/>
+      <c r="F79" s="77"/>
       <c r="G79" s="48"/>
       <c r="H79" s="49">
         <f t="shared" si="0"/>
@@ -4532,16 +4542,16 @@
       <c r="J79" s="51"/>
     </row>
     <row r="80" spans="1:10" ht="14" customHeight="1">
-      <c r="A80" s="81"/>
-      <c r="B80" s="140"/>
+      <c r="A80" s="94"/>
+      <c r="B80" s="122"/>
       <c r="C80" s="53">
         <v>9</v>
       </c>
-      <c r="D80" s="76" t="s">
+      <c r="D80" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="E80" s="74"/>
-      <c r="F80" s="75"/>
+      <c r="E80" s="76"/>
+      <c r="F80" s="77"/>
       <c r="G80" s="48"/>
       <c r="H80" s="49">
         <f t="shared" si="0"/>
@@ -4555,16 +4565,16 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="14" customHeight="1">
-      <c r="A81" s="82"/>
-      <c r="B81" s="140"/>
+      <c r="A81" s="95"/>
+      <c r="B81" s="122"/>
       <c r="C81" s="53">
         <v>10</v>
       </c>
-      <c r="D81" s="76" t="s">
+      <c r="D81" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="E81" s="74"/>
-      <c r="F81" s="75"/>
+      <c r="E81" s="76"/>
+      <c r="F81" s="77"/>
       <c r="G81" s="48"/>
       <c r="H81" s="49">
         <f t="shared" si="0"/>
@@ -4578,34 +4588,34 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="22" customHeight="1">
-      <c r="A82" s="111" t="s">
+      <c r="A82" s="128" t="s">
         <v>137</v>
       </c>
-      <c r="B82" s="112"/>
-      <c r="C82" s="112"/>
-      <c r="D82" s="112"/>
-      <c r="E82" s="112"/>
-      <c r="F82" s="112"/>
-      <c r="G82" s="112"/>
-      <c r="H82" s="112"/>
-      <c r="I82" s="112"/>
-      <c r="J82" s="113"/>
+      <c r="B82" s="123"/>
+      <c r="C82" s="123"/>
+      <c r="D82" s="123"/>
+      <c r="E82" s="123"/>
+      <c r="F82" s="123"/>
+      <c r="G82" s="123"/>
+      <c r="H82" s="123"/>
+      <c r="I82" s="123"/>
+      <c r="J82" s="124"/>
     </row>
     <row r="83" spans="1:10" ht="13" customHeight="1">
-      <c r="A83" s="155" t="s">
+      <c r="A83" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="B83" s="108" t="s">
+      <c r="B83" s="129" t="s">
         <v>138</v>
       </c>
       <c r="C83" s="54">
         <v>1</v>
       </c>
-      <c r="D83" s="92" t="s">
+      <c r="D83" s="118" t="s">
         <v>139</v>
       </c>
-      <c r="E83" s="74"/>
-      <c r="F83" s="75"/>
+      <c r="E83" s="76"/>
+      <c r="F83" s="77"/>
       <c r="G83" s="48" t="s">
         <v>140</v>
       </c>
@@ -4617,16 +4627,16 @@
       <c r="J83" s="57"/>
     </row>
     <row r="84" spans="1:10" ht="42" customHeight="1">
-      <c r="A84" s="97"/>
-      <c r="B84" s="81"/>
+      <c r="A84" s="100"/>
+      <c r="B84" s="94"/>
       <c r="C84" s="54">
         <v>2</v>
       </c>
-      <c r="D84" s="86" t="s">
+      <c r="D84" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="E84" s="74"/>
-      <c r="F84" s="75"/>
+      <c r="E84" s="76"/>
+      <c r="F84" s="77"/>
       <c r="G84" s="48" t="s">
         <v>140</v>
       </c>
@@ -4640,16 +4650,16 @@
       <c r="J84" s="59"/>
     </row>
     <row r="85" spans="1:10" ht="56" customHeight="1">
-      <c r="A85" s="97"/>
-      <c r="B85" s="81"/>
+      <c r="A85" s="100"/>
+      <c r="B85" s="94"/>
       <c r="C85" s="54">
         <v>3</v>
       </c>
-      <c r="D85" s="86" t="s">
+      <c r="D85" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="E85" s="74"/>
-      <c r="F85" s="75"/>
+      <c r="E85" s="76"/>
+      <c r="F85" s="77"/>
       <c r="G85" s="48" t="s">
         <v>140</v>
       </c>
@@ -4663,16 +4673,16 @@
       <c r="J85" s="59"/>
     </row>
     <row r="86" spans="1:10" ht="13" customHeight="1">
-      <c r="A86" s="97"/>
-      <c r="B86" s="81"/>
+      <c r="A86" s="100"/>
+      <c r="B86" s="94"/>
       <c r="C86" s="54">
         <v>4</v>
       </c>
-      <c r="D86" s="86" t="s">
+      <c r="D86" s="75" t="s">
         <v>145</v>
       </c>
-      <c r="E86" s="74"/>
-      <c r="F86" s="75"/>
+      <c r="E86" s="76"/>
+      <c r="F86" s="77"/>
       <c r="G86" s="48" t="s">
         <v>140</v>
       </c>
@@ -4684,16 +4694,16 @@
       <c r="J86" s="61"/>
     </row>
     <row r="87" spans="1:10" ht="13" customHeight="1">
-      <c r="A87" s="97"/>
-      <c r="B87" s="81"/>
+      <c r="A87" s="100"/>
+      <c r="B87" s="94"/>
       <c r="C87" s="54">
         <v>5</v>
       </c>
-      <c r="D87" s="86" t="s">
+      <c r="D87" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="E87" s="74"/>
-      <c r="F87" s="75"/>
+      <c r="E87" s="76"/>
+      <c r="F87" s="77"/>
       <c r="G87" s="48" t="s">
         <v>140</v>
       </c>
@@ -4705,16 +4715,16 @@
       <c r="J87" s="59"/>
     </row>
     <row r="88" spans="1:10" ht="13" customHeight="1">
-      <c r="A88" s="97"/>
-      <c r="B88" s="81"/>
+      <c r="A88" s="100"/>
+      <c r="B88" s="94"/>
       <c r="C88" s="54">
         <v>6</v>
       </c>
-      <c r="D88" s="86" t="s">
+      <c r="D88" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="E88" s="74"/>
-      <c r="F88" s="75"/>
+      <c r="E88" s="76"/>
+      <c r="F88" s="77"/>
       <c r="G88" s="48" t="s">
         <v>140</v>
       </c>
@@ -4726,16 +4736,16 @@
       <c r="J88" s="61"/>
     </row>
     <row r="89" spans="1:10" ht="13" customHeight="1">
-      <c r="A89" s="97"/>
-      <c r="B89" s="81"/>
+      <c r="A89" s="100"/>
+      <c r="B89" s="94"/>
       <c r="C89" s="54">
         <v>7</v>
       </c>
-      <c r="D89" s="76" t="s">
+      <c r="D89" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="E89" s="74"/>
-      <c r="F89" s="75"/>
+      <c r="E89" s="76"/>
+      <c r="F89" s="77"/>
       <c r="G89" s="48" t="s">
         <v>140</v>
       </c>
@@ -4747,16 +4757,16 @@
       <c r="J89" s="61"/>
     </row>
     <row r="90" spans="1:10" ht="13" customHeight="1">
-      <c r="A90" s="97"/>
-      <c r="B90" s="82"/>
+      <c r="A90" s="100"/>
+      <c r="B90" s="95"/>
       <c r="C90" s="54">
         <v>8</v>
       </c>
-      <c r="D90" s="76" t="s">
+      <c r="D90" s="81" t="s">
         <v>149</v>
       </c>
-      <c r="E90" s="74"/>
-      <c r="F90" s="75"/>
+      <c r="E90" s="76"/>
+      <c r="F90" s="77"/>
       <c r="G90" s="48"/>
       <c r="H90" s="49">
         <f t="shared" si="1"/>
@@ -4766,18 +4776,18 @@
       <c r="J90" s="61"/>
     </row>
     <row r="91" spans="1:10" ht="13" customHeight="1">
-      <c r="A91" s="97"/>
-      <c r="B91" s="108" t="s">
+      <c r="A91" s="100"/>
+      <c r="B91" s="129" t="s">
         <v>150</v>
       </c>
       <c r="C91" s="54">
         <v>9</v>
       </c>
-      <c r="D91" s="86" t="s">
+      <c r="D91" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="E91" s="74"/>
-      <c r="F91" s="75"/>
+      <c r="E91" s="76"/>
+      <c r="F91" s="77"/>
       <c r="G91" s="48" t="s">
         <v>152</v>
       </c>
@@ -4789,16 +4799,16 @@
       <c r="J91" s="59"/>
     </row>
     <row r="92" spans="1:10" ht="13" customHeight="1">
-      <c r="A92" s="97"/>
-      <c r="B92" s="81"/>
+      <c r="A92" s="100"/>
+      <c r="B92" s="94"/>
       <c r="C92" s="54">
         <v>10</v>
       </c>
-      <c r="D92" s="92" t="s">
+      <c r="D92" s="118" t="s">
         <v>153</v>
       </c>
-      <c r="E92" s="74"/>
-      <c r="F92" s="75"/>
+      <c r="E92" s="76"/>
+      <c r="F92" s="77"/>
       <c r="G92" s="48" t="s">
         <v>140</v>
       </c>
@@ -4810,16 +4820,16 @@
       <c r="J92" s="61"/>
     </row>
     <row r="93" spans="1:10" ht="13" customHeight="1">
-      <c r="A93" s="97"/>
-      <c r="B93" s="81"/>
+      <c r="A93" s="100"/>
+      <c r="B93" s="94"/>
       <c r="C93" s="54">
         <v>11</v>
       </c>
-      <c r="D93" s="92" t="s">
+      <c r="D93" s="118" t="s">
         <v>154</v>
       </c>
-      <c r="E93" s="74"/>
-      <c r="F93" s="75"/>
+      <c r="E93" s="76"/>
+      <c r="F93" s="77"/>
       <c r="G93" s="48" t="s">
         <v>140</v>
       </c>
@@ -4831,16 +4841,16 @@
       <c r="J93" s="63"/>
     </row>
     <row r="94" spans="1:10" ht="13" customHeight="1">
-      <c r="A94" s="97"/>
-      <c r="B94" s="81"/>
+      <c r="A94" s="100"/>
+      <c r="B94" s="94"/>
       <c r="C94" s="54">
         <v>12</v>
       </c>
-      <c r="D94" s="86" t="s">
+      <c r="D94" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="E94" s="74"/>
-      <c r="F94" s="75"/>
+      <c r="E94" s="76"/>
+      <c r="F94" s="77"/>
       <c r="G94" s="48" t="s">
         <v>140</v>
       </c>
@@ -4852,16 +4862,16 @@
       <c r="J94" s="65"/>
     </row>
     <row r="95" spans="1:10" ht="13" customHeight="1">
-      <c r="A95" s="97"/>
-      <c r="B95" s="82"/>
+      <c r="A95" s="100"/>
+      <c r="B95" s="95"/>
       <c r="C95" s="54">
         <v>13</v>
       </c>
-      <c r="D95" s="92" t="s">
+      <c r="D95" s="118" t="s">
         <v>156</v>
       </c>
-      <c r="E95" s="74"/>
-      <c r="F95" s="75"/>
+      <c r="E95" s="76"/>
+      <c r="F95" s="77"/>
       <c r="G95" s="48" t="s">
         <v>140</v>
       </c>
@@ -4873,16 +4883,16 @@
       <c r="J95" s="64"/>
     </row>
     <row r="96" spans="1:10" ht="13" customHeight="1">
-      <c r="A96" s="97"/>
+      <c r="A96" s="100"/>
       <c r="B96" s="66"/>
       <c r="C96" s="67">
         <v>14</v>
       </c>
-      <c r="D96" s="86" t="s">
+      <c r="D96" s="75" t="s">
         <v>157</v>
       </c>
-      <c r="E96" s="74"/>
-      <c r="F96" s="75"/>
+      <c r="E96" s="76"/>
+      <c r="F96" s="77"/>
       <c r="G96" s="48" t="s">
         <v>158</v>
       </c>
@@ -4894,16 +4904,16 @@
       <c r="J96" s="65"/>
     </row>
     <row r="97" spans="1:10" ht="13" customHeight="1">
-      <c r="A97" s="97"/>
+      <c r="A97" s="100"/>
       <c r="B97" s="66"/>
       <c r="C97" s="67">
         <v>15</v>
       </c>
-      <c r="D97" s="86" t="s">
+      <c r="D97" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="E97" s="74"/>
-      <c r="F97" s="75"/>
+      <c r="E97" s="76"/>
+      <c r="F97" s="77"/>
       <c r="G97" s="48" t="s">
         <v>152</v>
       </c>
@@ -4915,16 +4925,16 @@
       <c r="J97" s="65"/>
     </row>
     <row r="98" spans="1:10" ht="13" customHeight="1">
-      <c r="A98" s="97"/>
+      <c r="A98" s="100"/>
       <c r="B98" s="66"/>
       <c r="C98" s="67">
         <v>16</v>
       </c>
-      <c r="D98" s="86" t="s">
+      <c r="D98" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="E98" s="74"/>
-      <c r="F98" s="75"/>
+      <c r="E98" s="76"/>
+      <c r="F98" s="77"/>
       <c r="G98" s="48" t="s">
         <v>140</v>
       </c>
@@ -4936,18 +4946,18 @@
       <c r="J98" s="64"/>
     </row>
     <row r="99" spans="1:10" ht="13" customHeight="1">
-      <c r="A99" s="97"/>
+      <c r="A99" s="100"/>
       <c r="B99" s="66" t="s">
         <v>161</v>
       </c>
       <c r="C99" s="67">
         <v>17</v>
       </c>
-      <c r="D99" s="86" t="s">
+      <c r="D99" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="E99" s="74"/>
-      <c r="F99" s="75"/>
+      <c r="E99" s="76"/>
+      <c r="F99" s="77"/>
       <c r="G99" s="48" t="s">
         <v>140</v>
       </c>
@@ -4959,16 +4969,16 @@
       <c r="J99" s="64"/>
     </row>
     <row r="100" spans="1:10" ht="13" customHeight="1">
-      <c r="A100" s="97"/>
+      <c r="A100" s="100"/>
       <c r="B100" s="66"/>
       <c r="C100" s="67">
         <v>18</v>
       </c>
-      <c r="D100" s="86" t="s">
+      <c r="D100" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="E100" s="74"/>
-      <c r="F100" s="75"/>
+      <c r="E100" s="76"/>
+      <c r="F100" s="77"/>
       <c r="G100" s="48" t="s">
         <v>152</v>
       </c>
@@ -4980,16 +4990,16 @@
       <c r="J100" s="65"/>
     </row>
     <row r="101" spans="1:10" ht="13" customHeight="1">
-      <c r="A101" s="97"/>
+      <c r="A101" s="100"/>
       <c r="B101" s="66"/>
       <c r="C101" s="67">
         <v>19</v>
       </c>
-      <c r="D101" s="76" t="s">
+      <c r="D101" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="E101" s="74"/>
-      <c r="F101" s="75"/>
+      <c r="E101" s="76"/>
+      <c r="F101" s="77"/>
       <c r="G101" s="48" t="s">
         <v>140</v>
       </c>
@@ -5001,16 +5011,16 @@
       <c r="J101" s="65"/>
     </row>
     <row r="102" spans="1:10" ht="13" customHeight="1">
-      <c r="A102" s="97"/>
+      <c r="A102" s="100"/>
       <c r="B102" s="66"/>
       <c r="C102" s="67">
         <v>20</v>
       </c>
-      <c r="D102" s="76" t="s">
+      <c r="D102" s="81" t="s">
         <v>165</v>
       </c>
-      <c r="E102" s="74"/>
-      <c r="F102" s="75"/>
+      <c r="E102" s="76"/>
+      <c r="F102" s="77"/>
       <c r="G102" s="48" t="s">
         <v>152</v>
       </c>
@@ -5022,16 +5032,16 @@
       <c r="J102" s="65"/>
     </row>
     <row r="103" spans="1:10" ht="13" customHeight="1">
-      <c r="A103" s="97"/>
+      <c r="A103" s="100"/>
       <c r="B103" s="66"/>
       <c r="C103" s="67">
         <v>21</v>
       </c>
-      <c r="D103" s="76" t="s">
+      <c r="D103" s="81" t="s">
         <v>166</v>
       </c>
-      <c r="E103" s="74"/>
-      <c r="F103" s="75"/>
+      <c r="E103" s="76"/>
+      <c r="F103" s="77"/>
       <c r="G103" s="48" t="s">
         <v>140</v>
       </c>
@@ -5043,16 +5053,16 @@
       <c r="J103" s="65"/>
     </row>
     <row r="104" spans="1:10" ht="13" customHeight="1">
-      <c r="A104" s="141"/>
+      <c r="A104" s="101"/>
       <c r="B104" s="66"/>
       <c r="C104" s="67">
         <v>22</v>
       </c>
-      <c r="D104" s="76" t="s">
+      <c r="D104" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="E104" s="74"/>
-      <c r="F104" s="75"/>
+      <c r="E104" s="76"/>
+      <c r="F104" s="77"/>
       <c r="G104" s="48" t="s">
         <v>158</v>
       </c>
@@ -5064,20 +5074,20 @@
       <c r="J104" s="65"/>
     </row>
     <row r="105" spans="1:10" ht="13" customHeight="1">
-      <c r="A105" s="156" t="s">
+      <c r="A105" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="B105" s="151" t="s">
+      <c r="B105" s="90" t="s">
         <v>168</v>
       </c>
       <c r="C105" s="67">
         <v>1</v>
       </c>
-      <c r="D105" s="86" t="s">
+      <c r="D105" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="E105" s="74"/>
-      <c r="F105" s="75"/>
+      <c r="E105" s="76"/>
+      <c r="F105" s="77"/>
       <c r="G105" s="48" t="s">
         <v>140</v>
       </c>
@@ -5089,16 +5099,16 @@
       <c r="J105" s="65"/>
     </row>
     <row r="106" spans="1:10" ht="13" customHeight="1">
-      <c r="A106" s="84"/>
-      <c r="B106" s="84"/>
+      <c r="A106" s="91"/>
+      <c r="B106" s="91"/>
       <c r="C106" s="67">
         <v>2</v>
       </c>
-      <c r="D106" s="86" t="s">
+      <c r="D106" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="E106" s="74"/>
-      <c r="F106" s="75"/>
+      <c r="E106" s="76"/>
+      <c r="F106" s="77"/>
       <c r="G106" s="48" t="s">
         <v>152</v>
       </c>
@@ -5110,16 +5120,16 @@
       <c r="J106" s="65"/>
     </row>
     <row r="107" spans="1:10" ht="13" customHeight="1">
-      <c r="A107" s="84"/>
-      <c r="B107" s="84"/>
+      <c r="A107" s="91"/>
+      <c r="B107" s="91"/>
       <c r="C107" s="67">
         <v>3</v>
       </c>
-      <c r="D107" s="92" t="s">
+      <c r="D107" s="118" t="s">
         <v>171</v>
       </c>
-      <c r="E107" s="74"/>
-      <c r="F107" s="75"/>
+      <c r="E107" s="76"/>
+      <c r="F107" s="77"/>
       <c r="G107" s="48" t="s">
         <v>140</v>
       </c>
@@ -5131,16 +5141,16 @@
       <c r="J107" s="64"/>
     </row>
     <row r="108" spans="1:10" ht="13" customHeight="1">
-      <c r="A108" s="84"/>
-      <c r="B108" s="84"/>
+      <c r="A108" s="91"/>
+      <c r="B108" s="91"/>
       <c r="C108" s="67">
         <v>4</v>
       </c>
-      <c r="D108" s="86" t="s">
+      <c r="D108" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="E108" s="74"/>
-      <c r="F108" s="75"/>
+      <c r="E108" s="76"/>
+      <c r="F108" s="77"/>
       <c r="G108" s="48" t="s">
         <v>140</v>
       </c>
@@ -5152,16 +5162,16 @@
       <c r="J108" s="64"/>
     </row>
     <row r="109" spans="1:10" ht="13" customHeight="1">
-      <c r="A109" s="84"/>
-      <c r="B109" s="84"/>
+      <c r="A109" s="91"/>
+      <c r="B109" s="91"/>
       <c r="C109" s="67">
         <v>5</v>
       </c>
-      <c r="D109" s="92" t="s">
+      <c r="D109" s="118" t="s">
         <v>173</v>
       </c>
-      <c r="E109" s="74"/>
-      <c r="F109" s="75"/>
+      <c r="E109" s="76"/>
+      <c r="F109" s="77"/>
       <c r="G109" s="48" t="s">
         <v>140</v>
       </c>
@@ -5173,16 +5183,16 @@
       <c r="J109" s="64"/>
     </row>
     <row r="110" spans="1:10" ht="13" customHeight="1">
-      <c r="A110" s="84"/>
-      <c r="B110" s="84"/>
+      <c r="A110" s="91"/>
+      <c r="B110" s="91"/>
       <c r="C110" s="67">
         <v>6</v>
       </c>
-      <c r="D110" s="92" t="s">
+      <c r="D110" s="118" t="s">
         <v>174</v>
       </c>
-      <c r="E110" s="74"/>
-      <c r="F110" s="75"/>
+      <c r="E110" s="76"/>
+      <c r="F110" s="77"/>
       <c r="G110" s="48" t="s">
         <v>158</v>
       </c>
@@ -5194,16 +5204,16 @@
       <c r="J110" s="65"/>
     </row>
     <row r="111" spans="1:10" ht="13" customHeight="1">
-      <c r="A111" s="84"/>
-      <c r="B111" s="84"/>
+      <c r="A111" s="91"/>
+      <c r="B111" s="91"/>
       <c r="C111" s="67">
         <v>7</v>
       </c>
-      <c r="D111" s="92" t="s">
+      <c r="D111" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="E111" s="74"/>
-      <c r="F111" s="75"/>
+      <c r="E111" s="76"/>
+      <c r="F111" s="77"/>
       <c r="G111" s="48" t="s">
         <v>140</v>
       </c>
@@ -5215,16 +5225,16 @@
       <c r="J111" s="64"/>
     </row>
     <row r="112" spans="1:10" ht="13" customHeight="1">
-      <c r="A112" s="84"/>
-      <c r="B112" s="84"/>
+      <c r="A112" s="91"/>
+      <c r="B112" s="91"/>
       <c r="C112" s="67">
         <v>8</v>
       </c>
-      <c r="D112" s="92" t="s">
+      <c r="D112" s="118" t="s">
         <v>176</v>
       </c>
-      <c r="E112" s="74"/>
-      <c r="F112" s="75"/>
+      <c r="E112" s="76"/>
+      <c r="F112" s="77"/>
       <c r="G112" s="48" t="s">
         <v>152</v>
       </c>
@@ -5236,16 +5246,16 @@
       <c r="J112" s="65"/>
     </row>
     <row r="113" spans="1:10" ht="13" customHeight="1">
-      <c r="A113" s="84"/>
-      <c r="B113" s="84"/>
+      <c r="A113" s="91"/>
+      <c r="B113" s="91"/>
       <c r="C113" s="67">
         <v>9</v>
       </c>
-      <c r="D113" s="92" t="s">
+      <c r="D113" s="118" t="s">
         <v>177</v>
       </c>
-      <c r="E113" s="74"/>
-      <c r="F113" s="75"/>
+      <c r="E113" s="76"/>
+      <c r="F113" s="77"/>
       <c r="G113" s="48" t="s">
         <v>140</v>
       </c>
@@ -5257,16 +5267,16 @@
       <c r="J113" s="65"/>
     </row>
     <row r="114" spans="1:10" ht="13" customHeight="1">
-      <c r="A114" s="84"/>
-      <c r="B114" s="84"/>
+      <c r="A114" s="91"/>
+      <c r="B114" s="91"/>
       <c r="C114" s="67">
         <v>10</v>
       </c>
-      <c r="D114" s="92" t="s">
+      <c r="D114" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="E114" s="74"/>
-      <c r="F114" s="75"/>
+      <c r="E114" s="76"/>
+      <c r="F114" s="77"/>
       <c r="G114" s="48" t="s">
         <v>140</v>
       </c>
@@ -5278,16 +5288,16 @@
       <c r="J114" s="65"/>
     </row>
     <row r="115" spans="1:10" ht="13" customHeight="1">
-      <c r="A115" s="84"/>
-      <c r="B115" s="84"/>
+      <c r="A115" s="91"/>
+      <c r="B115" s="91"/>
       <c r="C115" s="67">
         <v>11</v>
       </c>
-      <c r="D115" s="86" t="s">
+      <c r="D115" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="E115" s="74"/>
-      <c r="F115" s="75"/>
+      <c r="E115" s="76"/>
+      <c r="F115" s="77"/>
       <c r="G115" s="48" t="s">
         <v>158</v>
       </c>
@@ -5299,16 +5309,16 @@
       <c r="J115" s="65"/>
     </row>
     <row r="116" spans="1:10" ht="13" customHeight="1">
-      <c r="A116" s="84"/>
-      <c r="B116" s="85"/>
+      <c r="A116" s="91"/>
+      <c r="B116" s="92"/>
       <c r="C116" s="67">
         <v>12</v>
       </c>
-      <c r="D116" s="86" t="s">
+      <c r="D116" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="E116" s="74"/>
-      <c r="F116" s="75"/>
+      <c r="E116" s="76"/>
+      <c r="F116" s="77"/>
       <c r="G116" s="48" t="s">
         <v>140</v>
       </c>
@@ -5320,18 +5330,18 @@
       <c r="J116" s="65"/>
     </row>
     <row r="117" spans="1:10" ht="13" customHeight="1">
-      <c r="A117" s="84"/>
-      <c r="B117" s="88" t="s">
+      <c r="A117" s="91"/>
+      <c r="B117" s="138" t="s">
         <v>181</v>
       </c>
       <c r="C117" s="67">
         <v>13</v>
       </c>
-      <c r="D117" s="76" t="s">
+      <c r="D117" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="E117" s="74"/>
-      <c r="F117" s="75"/>
+      <c r="E117" s="76"/>
+      <c r="F117" s="77"/>
       <c r="G117" s="48" t="s">
         <v>140</v>
       </c>
@@ -5343,16 +5353,16 @@
       <c r="J117" s="65"/>
     </row>
     <row r="118" spans="1:10" ht="13" customHeight="1">
-      <c r="A118" s="84"/>
-      <c r="B118" s="84"/>
+      <c r="A118" s="91"/>
+      <c r="B118" s="91"/>
       <c r="C118" s="67">
         <v>14</v>
       </c>
-      <c r="D118" s="76" t="s">
+      <c r="D118" s="81" t="s">
         <v>183</v>
       </c>
-      <c r="E118" s="74"/>
-      <c r="F118" s="75"/>
+      <c r="E118" s="76"/>
+      <c r="F118" s="77"/>
       <c r="G118" s="48" t="s">
         <v>140</v>
       </c>
@@ -5364,16 +5374,16 @@
       <c r="J118" s="64"/>
     </row>
     <row r="119" spans="1:10" ht="13" customHeight="1">
-      <c r="A119" s="84"/>
-      <c r="B119" s="85"/>
+      <c r="A119" s="91"/>
+      <c r="B119" s="92"/>
       <c r="C119" s="67">
         <v>15</v>
       </c>
-      <c r="D119" s="76" t="s">
+      <c r="D119" s="81" t="s">
         <v>184</v>
       </c>
-      <c r="E119" s="74"/>
-      <c r="F119" s="75"/>
+      <c r="E119" s="76"/>
+      <c r="F119" s="77"/>
       <c r="G119" s="48" t="s">
         <v>140</v>
       </c>
@@ -5385,18 +5395,18 @@
       <c r="J119" s="64"/>
     </row>
     <row r="120" spans="1:10" ht="13" customHeight="1">
-      <c r="A120" s="84"/>
-      <c r="B120" s="88" t="s">
+      <c r="A120" s="91"/>
+      <c r="B120" s="138" t="s">
         <v>185</v>
       </c>
       <c r="C120" s="67">
         <v>16</v>
       </c>
-      <c r="D120" s="86" t="s">
+      <c r="D120" s="75" t="s">
         <v>186</v>
       </c>
-      <c r="E120" s="74"/>
-      <c r="F120" s="75"/>
+      <c r="E120" s="76"/>
+      <c r="F120" s="77"/>
       <c r="G120" s="48" t="s">
         <v>140</v>
       </c>
@@ -5408,16 +5418,16 @@
       <c r="J120" s="64"/>
     </row>
     <row r="121" spans="1:10" ht="13" customHeight="1">
-      <c r="A121" s="84"/>
-      <c r="B121" s="84"/>
+      <c r="A121" s="91"/>
+      <c r="B121" s="91"/>
       <c r="C121" s="67">
         <v>17</v>
       </c>
-      <c r="D121" s="86" t="s">
+      <c r="D121" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="E121" s="74"/>
-      <c r="F121" s="75"/>
+      <c r="E121" s="76"/>
+      <c r="F121" s="77"/>
       <c r="G121" s="48" t="s">
         <v>140</v>
       </c>
@@ -5429,16 +5439,16 @@
       <c r="J121" s="64"/>
     </row>
     <row r="122" spans="1:10" ht="13" customHeight="1">
-      <c r="A122" s="84"/>
-      <c r="B122" s="85"/>
+      <c r="A122" s="91"/>
+      <c r="B122" s="92"/>
       <c r="C122" s="67">
         <v>18</v>
       </c>
-      <c r="D122" s="76" t="s">
+      <c r="D122" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="E122" s="74"/>
-      <c r="F122" s="75"/>
+      <c r="E122" s="76"/>
+      <c r="F122" s="77"/>
       <c r="G122" s="48" t="s">
         <v>140</v>
       </c>
@@ -5450,18 +5460,18 @@
       <c r="J122" s="65"/>
     </row>
     <row r="123" spans="1:10" ht="13" customHeight="1">
-      <c r="A123" s="84"/>
-      <c r="B123" s="88" t="s">
+      <c r="A123" s="91"/>
+      <c r="B123" s="138" t="s">
         <v>189</v>
       </c>
       <c r="C123" s="67">
         <v>19</v>
       </c>
-      <c r="D123" s="86" t="s">
+      <c r="D123" s="75" t="s">
         <v>190</v>
       </c>
-      <c r="E123" s="74"/>
-      <c r="F123" s="75"/>
+      <c r="E123" s="76"/>
+      <c r="F123" s="77"/>
       <c r="G123" s="48" t="s">
         <v>140</v>
       </c>
@@ -5473,16 +5483,16 @@
       <c r="J123" s="64"/>
     </row>
     <row r="124" spans="1:10" ht="13" customHeight="1">
-      <c r="A124" s="84"/>
-      <c r="B124" s="84"/>
+      <c r="A124" s="91"/>
+      <c r="B124" s="91"/>
       <c r="C124" s="67">
         <v>20</v>
       </c>
-      <c r="D124" s="86" t="s">
+      <c r="D124" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="E124" s="74"/>
-      <c r="F124" s="75"/>
+      <c r="E124" s="76"/>
+      <c r="F124" s="77"/>
       <c r="G124" s="48" t="s">
         <v>152</v>
       </c>
@@ -5494,16 +5504,16 @@
       <c r="J124" s="64"/>
     </row>
     <row r="125" spans="1:10" ht="13" customHeight="1">
-      <c r="A125" s="84"/>
-      <c r="B125" s="85"/>
+      <c r="A125" s="91"/>
+      <c r="B125" s="92"/>
       <c r="C125" s="67">
         <v>21</v>
       </c>
-      <c r="D125" s="86" t="s">
+      <c r="D125" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="E125" s="74"/>
-      <c r="F125" s="75"/>
+      <c r="E125" s="76"/>
+      <c r="F125" s="77"/>
       <c r="G125" s="48" t="s">
         <v>140</v>
       </c>
@@ -5515,18 +5525,18 @@
       <c r="J125" s="64"/>
     </row>
     <row r="126" spans="1:10" ht="13" customHeight="1">
-      <c r="A126" s="84"/>
-      <c r="B126" s="88" t="s">
+      <c r="A126" s="91"/>
+      <c r="B126" s="138" t="s">
         <v>193</v>
       </c>
       <c r="C126" s="67">
         <v>22</v>
       </c>
-      <c r="D126" s="86" t="s">
+      <c r="D126" s="75" t="s">
         <v>194</v>
       </c>
-      <c r="E126" s="74"/>
-      <c r="F126" s="75"/>
+      <c r="E126" s="76"/>
+      <c r="F126" s="77"/>
       <c r="G126" s="48" t="s">
         <v>140</v>
       </c>
@@ -5538,16 +5548,16 @@
       <c r="J126" s="64"/>
     </row>
     <row r="127" spans="1:10" ht="13" customHeight="1">
-      <c r="A127" s="84"/>
-      <c r="B127" s="84"/>
+      <c r="A127" s="91"/>
+      <c r="B127" s="91"/>
       <c r="C127" s="67">
         <v>23</v>
       </c>
-      <c r="D127" s="86" t="s">
+      <c r="D127" s="75" t="s">
         <v>195</v>
       </c>
-      <c r="E127" s="74"/>
-      <c r="F127" s="75"/>
+      <c r="E127" s="76"/>
+      <c r="F127" s="77"/>
       <c r="G127" s="48" t="s">
         <v>140</v>
       </c>
@@ -5559,16 +5569,16 @@
       <c r="J127" s="64"/>
     </row>
     <row r="128" spans="1:10" ht="13" customHeight="1">
-      <c r="A128" s="84"/>
-      <c r="B128" s="84"/>
+      <c r="A128" s="91"/>
+      <c r="B128" s="91"/>
       <c r="C128" s="67">
         <v>24</v>
       </c>
-      <c r="D128" s="92" t="s">
+      <c r="D128" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="E128" s="74"/>
-      <c r="F128" s="75"/>
+      <c r="E128" s="76"/>
+      <c r="F128" s="77"/>
       <c r="G128" s="48" t="s">
         <v>140</v>
       </c>
@@ -5580,16 +5590,16 @@
       <c r="J128" s="64"/>
     </row>
     <row r="129" spans="1:10" ht="13" customHeight="1">
-      <c r="A129" s="85"/>
-      <c r="B129" s="85"/>
+      <c r="A129" s="92"/>
+      <c r="B129" s="92"/>
       <c r="C129" s="67">
         <v>25</v>
       </c>
-      <c r="D129" s="92" t="s">
+      <c r="D129" s="118" t="s">
         <v>197</v>
       </c>
-      <c r="E129" s="74"/>
-      <c r="F129" s="75"/>
+      <c r="E129" s="76"/>
+      <c r="F129" s="77"/>
       <c r="G129" s="48" t="s">
         <v>152</v>
       </c>
@@ -5601,20 +5611,20 @@
       <c r="J129" s="65"/>
     </row>
     <row r="130" spans="1:10" ht="13" customHeight="1">
-      <c r="A130" s="96" t="s">
+      <c r="A130" s="147" t="s">
         <v>198</v>
       </c>
-      <c r="B130" s="87" t="s">
+      <c r="B130" s="93" t="s">
         <v>199</v>
       </c>
       <c r="C130" s="54">
         <v>1</v>
       </c>
-      <c r="D130" s="86" t="s">
+      <c r="D130" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="E130" s="74"/>
-      <c r="F130" s="75"/>
+      <c r="E130" s="76"/>
+      <c r="F130" s="77"/>
       <c r="G130" s="48" t="s">
         <v>140</v>
       </c>
@@ -5626,16 +5636,16 @@
       <c r="J130" s="50"/>
     </row>
     <row r="131" spans="1:10" ht="13" customHeight="1">
-      <c r="A131" s="97"/>
-      <c r="B131" s="81"/>
+      <c r="A131" s="100"/>
+      <c r="B131" s="94"/>
       <c r="C131" s="54">
         <v>2</v>
       </c>
-      <c r="D131" s="86" t="s">
+      <c r="D131" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="E131" s="74"/>
-      <c r="F131" s="75"/>
+      <c r="E131" s="76"/>
+      <c r="F131" s="77"/>
       <c r="G131" s="48" t="s">
         <v>140</v>
       </c>
@@ -5647,16 +5657,16 @@
       <c r="J131" s="50"/>
     </row>
     <row r="132" spans="1:10" ht="13" customHeight="1">
-      <c r="A132" s="97"/>
-      <c r="B132" s="81"/>
+      <c r="A132" s="100"/>
+      <c r="B132" s="94"/>
       <c r="C132" s="54">
         <v>3</v>
       </c>
-      <c r="D132" s="86" t="s">
+      <c r="D132" s="75" t="s">
         <v>202</v>
       </c>
-      <c r="E132" s="74"/>
-      <c r="F132" s="75"/>
+      <c r="E132" s="76"/>
+      <c r="F132" s="77"/>
       <c r="G132" s="48" t="s">
         <v>140</v>
       </c>
@@ -5668,16 +5678,16 @@
       <c r="J132" s="50"/>
     </row>
     <row r="133" spans="1:10" ht="13" customHeight="1">
-      <c r="A133" s="97"/>
-      <c r="B133" s="81"/>
+      <c r="A133" s="100"/>
+      <c r="B133" s="94"/>
       <c r="C133" s="54">
         <v>4</v>
       </c>
-      <c r="D133" s="86" t="s">
+      <c r="D133" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="E133" s="74"/>
-      <c r="F133" s="75"/>
+      <c r="E133" s="76"/>
+      <c r="F133" s="77"/>
       <c r="G133" s="48" t="s">
         <v>158</v>
       </c>
@@ -5689,16 +5699,16 @@
       <c r="J133" s="50"/>
     </row>
     <row r="134" spans="1:10" ht="13" customHeight="1">
-      <c r="A134" s="97"/>
-      <c r="B134" s="82"/>
+      <c r="A134" s="100"/>
+      <c r="B134" s="95"/>
       <c r="C134" s="54">
         <v>5</v>
       </c>
-      <c r="D134" s="86" t="s">
+      <c r="D134" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="E134" s="74"/>
-      <c r="F134" s="75"/>
+      <c r="E134" s="76"/>
+      <c r="F134" s="77"/>
       <c r="G134" s="48" t="s">
         <v>152</v>
       </c>
@@ -5710,18 +5720,18 @@
       <c r="J134" s="50"/>
     </row>
     <row r="135" spans="1:10" ht="13" customHeight="1">
-      <c r="A135" s="97"/>
-      <c r="B135" s="87" t="s">
+      <c r="A135" s="100"/>
+      <c r="B135" s="93" t="s">
         <v>205</v>
       </c>
       <c r="C135" s="54">
         <v>6</v>
       </c>
-      <c r="D135" s="86" t="s">
+      <c r="D135" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="E135" s="74"/>
-      <c r="F135" s="75"/>
+      <c r="E135" s="76"/>
+      <c r="F135" s="77"/>
       <c r="G135" s="48" t="s">
         <v>140</v>
       </c>
@@ -5733,16 +5743,16 @@
       <c r="J135" s="50"/>
     </row>
     <row r="136" spans="1:10" ht="13" customHeight="1">
-      <c r="A136" s="97"/>
-      <c r="B136" s="81"/>
+      <c r="A136" s="100"/>
+      <c r="B136" s="94"/>
       <c r="C136" s="54">
         <v>7</v>
       </c>
-      <c r="D136" s="86" t="s">
+      <c r="D136" s="75" t="s">
         <v>207</v>
       </c>
-      <c r="E136" s="74"/>
-      <c r="F136" s="75"/>
+      <c r="E136" s="76"/>
+      <c r="F136" s="77"/>
       <c r="G136" s="48" t="s">
         <v>140</v>
       </c>
@@ -5754,16 +5764,16 @@
       <c r="J136" s="50"/>
     </row>
     <row r="137" spans="1:10" ht="13" customHeight="1">
-      <c r="A137" s="97"/>
-      <c r="B137" s="81"/>
+      <c r="A137" s="100"/>
+      <c r="B137" s="94"/>
       <c r="C137" s="54">
         <v>8</v>
       </c>
-      <c r="D137" s="86" t="s">
+      <c r="D137" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="E137" s="74"/>
-      <c r="F137" s="75"/>
+      <c r="E137" s="76"/>
+      <c r="F137" s="77"/>
       <c r="G137" s="48" t="s">
         <v>140</v>
       </c>
@@ -5775,16 +5785,16 @@
       <c r="J137" s="50"/>
     </row>
     <row r="138" spans="1:10" ht="13" customHeight="1">
-      <c r="A138" s="97"/>
-      <c r="B138" s="81"/>
+      <c r="A138" s="100"/>
+      <c r="B138" s="94"/>
       <c r="C138" s="54">
         <v>9</v>
       </c>
-      <c r="D138" s="86" t="s">
+      <c r="D138" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="E138" s="74"/>
-      <c r="F138" s="75"/>
+      <c r="E138" s="76"/>
+      <c r="F138" s="77"/>
       <c r="G138" s="48" t="s">
         <v>140</v>
       </c>
@@ -5796,16 +5806,16 @@
       <c r="J138" s="50"/>
     </row>
     <row r="139" spans="1:10" ht="13" customHeight="1">
-      <c r="A139" s="97"/>
-      <c r="B139" s="82"/>
+      <c r="A139" s="100"/>
+      <c r="B139" s="95"/>
       <c r="C139" s="54">
         <v>10</v>
       </c>
-      <c r="D139" s="86" t="s">
+      <c r="D139" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="E139" s="74"/>
-      <c r="F139" s="75"/>
+      <c r="E139" s="76"/>
+      <c r="F139" s="77"/>
       <c r="G139" s="48" t="s">
         <v>140</v>
       </c>
@@ -5817,18 +5827,18 @@
       <c r="J139" s="50"/>
     </row>
     <row r="140" spans="1:10" ht="13" customHeight="1">
-      <c r="A140" s="97"/>
-      <c r="B140" s="87" t="s">
+      <c r="A140" s="100"/>
+      <c r="B140" s="93" t="s">
         <v>211</v>
       </c>
       <c r="C140" s="54">
         <v>11</v>
       </c>
-      <c r="D140" s="86" t="s">
+      <c r="D140" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="E140" s="74"/>
-      <c r="F140" s="75"/>
+      <c r="E140" s="76"/>
+      <c r="F140" s="77"/>
       <c r="G140" s="48" t="s">
         <v>140</v>
       </c>
@@ -5840,16 +5850,16 @@
       <c r="J140" s="50"/>
     </row>
     <row r="141" spans="1:10" ht="13" customHeight="1">
-      <c r="A141" s="97"/>
-      <c r="B141" s="81"/>
+      <c r="A141" s="100"/>
+      <c r="B141" s="94"/>
       <c r="C141" s="54">
         <v>12</v>
       </c>
-      <c r="D141" s="86" t="s">
+      <c r="D141" s="75" t="s">
         <v>213</v>
       </c>
-      <c r="E141" s="74"/>
-      <c r="F141" s="75"/>
+      <c r="E141" s="76"/>
+      <c r="F141" s="77"/>
       <c r="G141" s="48" t="s">
         <v>140</v>
       </c>
@@ -5861,16 +5871,16 @@
       <c r="J141" s="50"/>
     </row>
     <row r="142" spans="1:10" ht="13" customHeight="1">
-      <c r="A142" s="97"/>
-      <c r="B142" s="81"/>
+      <c r="A142" s="100"/>
+      <c r="B142" s="94"/>
       <c r="C142" s="54">
         <v>13</v>
       </c>
-      <c r="D142" s="86" t="s">
+      <c r="D142" s="75" t="s">
         <v>214</v>
       </c>
-      <c r="E142" s="74"/>
-      <c r="F142" s="75"/>
+      <c r="E142" s="76"/>
+      <c r="F142" s="77"/>
       <c r="G142" s="48" t="s">
         <v>140</v>
       </c>
@@ -5882,16 +5892,16 @@
       <c r="J142" s="50"/>
     </row>
     <row r="143" spans="1:10" ht="13" customHeight="1">
-      <c r="A143" s="97"/>
-      <c r="B143" s="81"/>
+      <c r="A143" s="100"/>
+      <c r="B143" s="94"/>
       <c r="C143" s="54">
         <v>14</v>
       </c>
-      <c r="D143" s="86" t="s">
+      <c r="D143" s="75" t="s">
         <v>215</v>
       </c>
-      <c r="E143" s="74"/>
-      <c r="F143" s="75"/>
+      <c r="E143" s="76"/>
+      <c r="F143" s="77"/>
       <c r="G143" s="48" t="s">
         <v>140</v>
       </c>
@@ -5903,16 +5913,16 @@
       <c r="J143" s="50"/>
     </row>
     <row r="144" spans="1:10" ht="13" customHeight="1">
-      <c r="A144" s="97"/>
-      <c r="B144" s="81"/>
+      <c r="A144" s="100"/>
+      <c r="B144" s="94"/>
       <c r="C144" s="54">
         <v>15</v>
       </c>
-      <c r="D144" s="86" t="s">
+      <c r="D144" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="E144" s="74"/>
-      <c r="F144" s="75"/>
+      <c r="E144" s="76"/>
+      <c r="F144" s="77"/>
       <c r="G144" s="48" t="s">
         <v>140</v>
       </c>
@@ -5924,16 +5934,16 @@
       <c r="J144" s="50"/>
     </row>
     <row r="145" spans="1:10" ht="13" customHeight="1">
-      <c r="A145" s="97"/>
-      <c r="B145" s="81"/>
+      <c r="A145" s="100"/>
+      <c r="B145" s="94"/>
       <c r="C145" s="54">
         <v>16</v>
       </c>
-      <c r="D145" s="86" t="s">
+      <c r="D145" s="75" t="s">
         <v>217</v>
       </c>
-      <c r="E145" s="74"/>
-      <c r="F145" s="75"/>
+      <c r="E145" s="76"/>
+      <c r="F145" s="77"/>
       <c r="G145" s="48" t="s">
         <v>152</v>
       </c>
@@ -5945,16 +5955,16 @@
       <c r="J145" s="50"/>
     </row>
     <row r="146" spans="1:10" ht="13" customHeight="1">
-      <c r="A146" s="97"/>
-      <c r="B146" s="81"/>
+      <c r="A146" s="100"/>
+      <c r="B146" s="94"/>
       <c r="C146" s="54">
         <v>17</v>
       </c>
-      <c r="D146" s="86" t="s">
+      <c r="D146" s="75" t="s">
         <v>218</v>
       </c>
-      <c r="E146" s="74"/>
-      <c r="F146" s="75"/>
+      <c r="E146" s="76"/>
+      <c r="F146" s="77"/>
       <c r="G146" s="48" t="s">
         <v>140</v>
       </c>
@@ -5966,16 +5976,16 @@
       <c r="J146" s="50"/>
     </row>
     <row r="147" spans="1:10" ht="13" customHeight="1">
-      <c r="A147" s="97"/>
-      <c r="B147" s="81"/>
+      <c r="A147" s="100"/>
+      <c r="B147" s="94"/>
       <c r="C147" s="54">
         <v>18</v>
       </c>
-      <c r="D147" s="86" t="s">
+      <c r="D147" s="75" t="s">
         <v>219</v>
       </c>
-      <c r="E147" s="74"/>
-      <c r="F147" s="75"/>
+      <c r="E147" s="76"/>
+      <c r="F147" s="77"/>
       <c r="G147" s="48" t="s">
         <v>152</v>
       </c>
@@ -5987,16 +5997,16 @@
       <c r="J147" s="50"/>
     </row>
     <row r="148" spans="1:10" ht="13" customHeight="1">
-      <c r="A148" s="97"/>
-      <c r="B148" s="81"/>
+      <c r="A148" s="100"/>
+      <c r="B148" s="94"/>
       <c r="C148" s="54">
         <v>19</v>
       </c>
-      <c r="D148" s="86" t="s">
+      <c r="D148" s="75" t="s">
         <v>220</v>
       </c>
-      <c r="E148" s="74"/>
-      <c r="F148" s="75"/>
+      <c r="E148" s="76"/>
+      <c r="F148" s="77"/>
       <c r="G148" s="48" t="s">
         <v>140</v>
       </c>
@@ -6008,16 +6018,16 @@
       <c r="J148" s="50"/>
     </row>
     <row r="149" spans="1:10" ht="13" customHeight="1">
-      <c r="A149" s="97"/>
-      <c r="B149" s="81"/>
+      <c r="A149" s="100"/>
+      <c r="B149" s="94"/>
       <c r="C149" s="54">
         <v>20</v>
       </c>
-      <c r="D149" s="86" t="s">
+      <c r="D149" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="E149" s="74"/>
-      <c r="F149" s="75"/>
+      <c r="E149" s="76"/>
+      <c r="F149" s="77"/>
       <c r="G149" s="48" t="s">
         <v>140</v>
       </c>
@@ -6029,16 +6039,16 @@
       <c r="J149" s="50"/>
     </row>
     <row r="150" spans="1:10" ht="13" customHeight="1">
-      <c r="A150" s="97"/>
-      <c r="B150" s="81"/>
+      <c r="A150" s="100"/>
+      <c r="B150" s="94"/>
       <c r="C150" s="54">
         <v>21</v>
       </c>
-      <c r="D150" s="86" t="s">
+      <c r="D150" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="E150" s="74"/>
-      <c r="F150" s="75"/>
+      <c r="E150" s="76"/>
+      <c r="F150" s="77"/>
       <c r="G150" s="48" t="s">
         <v>140</v>
       </c>
@@ -6050,16 +6060,16 @@
       <c r="J150" s="50"/>
     </row>
     <row r="151" spans="1:10" ht="13" customHeight="1">
-      <c r="A151" s="97"/>
-      <c r="B151" s="81"/>
+      <c r="A151" s="100"/>
+      <c r="B151" s="94"/>
       <c r="C151" s="54">
         <v>22</v>
       </c>
-      <c r="D151" s="86" t="s">
+      <c r="D151" s="75" t="s">
         <v>223</v>
       </c>
-      <c r="E151" s="74"/>
-      <c r="F151" s="75"/>
+      <c r="E151" s="76"/>
+      <c r="F151" s="77"/>
       <c r="G151" s="48" t="s">
         <v>140</v>
       </c>
@@ -6071,16 +6081,16 @@
       <c r="J151" s="50"/>
     </row>
     <row r="152" spans="1:10" ht="13" customHeight="1">
-      <c r="A152" s="97"/>
-      <c r="B152" s="82"/>
+      <c r="A152" s="100"/>
+      <c r="B152" s="95"/>
       <c r="C152" s="54">
         <v>23</v>
       </c>
-      <c r="D152" s="86" t="s">
+      <c r="D152" s="75" t="s">
         <v>224</v>
       </c>
-      <c r="E152" s="74"/>
-      <c r="F152" s="75"/>
+      <c r="E152" s="76"/>
+      <c r="F152" s="77"/>
       <c r="G152" s="48" t="s">
         <v>152</v>
       </c>
@@ -6094,18 +6104,18 @@
       <c r="J152" s="50"/>
     </row>
     <row r="153" spans="1:10" ht="13" customHeight="1">
-      <c r="A153" s="97"/>
-      <c r="B153" s="87" t="s">
+      <c r="A153" s="100"/>
+      <c r="B153" s="93" t="s">
         <v>226</v>
       </c>
       <c r="C153" s="54">
         <v>24</v>
       </c>
-      <c r="D153" s="86" t="s">
+      <c r="D153" s="75" t="s">
         <v>227</v>
       </c>
-      <c r="E153" s="74"/>
-      <c r="F153" s="75"/>
+      <c r="E153" s="76"/>
+      <c r="F153" s="77"/>
       <c r="G153" s="48"/>
       <c r="H153" s="49">
         <f t="shared" si="3"/>
@@ -6117,16 +6127,16 @@
       <c r="J153" s="50"/>
     </row>
     <row r="154" spans="1:10" ht="13" customHeight="1">
-      <c r="A154" s="97"/>
-      <c r="B154" s="81"/>
+      <c r="A154" s="100"/>
+      <c r="B154" s="94"/>
       <c r="C154" s="54">
         <v>25</v>
       </c>
-      <c r="D154" s="86" t="s">
+      <c r="D154" s="75" t="s">
         <v>229</v>
       </c>
-      <c r="E154" s="74"/>
-      <c r="F154" s="75"/>
+      <c r="E154" s="76"/>
+      <c r="F154" s="77"/>
       <c r="G154" s="48"/>
       <c r="H154" s="49">
         <f t="shared" si="3"/>
@@ -6136,16 +6146,16 @@
       <c r="J154" s="50"/>
     </row>
     <row r="155" spans="1:10" ht="13" customHeight="1">
-      <c r="A155" s="97"/>
-      <c r="B155" s="81"/>
+      <c r="A155" s="100"/>
+      <c r="B155" s="94"/>
       <c r="C155" s="54">
         <v>26</v>
       </c>
-      <c r="D155" s="86" t="s">
+      <c r="D155" s="75" t="s">
         <v>230</v>
       </c>
-      <c r="E155" s="74"/>
-      <c r="F155" s="75"/>
+      <c r="E155" s="76"/>
+      <c r="F155" s="77"/>
       <c r="G155" s="48"/>
       <c r="H155" s="49">
         <f t="shared" si="3"/>
@@ -6155,16 +6165,16 @@
       <c r="J155" s="50"/>
     </row>
     <row r="156" spans="1:10" ht="13" customHeight="1">
-      <c r="A156" s="97"/>
-      <c r="B156" s="81"/>
+      <c r="A156" s="100"/>
+      <c r="B156" s="94"/>
       <c r="C156" s="54">
         <v>27</v>
       </c>
-      <c r="D156" s="86" t="s">
+      <c r="D156" s="75" t="s">
         <v>231</v>
       </c>
-      <c r="E156" s="74"/>
-      <c r="F156" s="75"/>
+      <c r="E156" s="76"/>
+      <c r="F156" s="77"/>
       <c r="G156" s="48"/>
       <c r="H156" s="49">
         <f t="shared" si="3"/>
@@ -6174,16 +6184,16 @@
       <c r="J156" s="50"/>
     </row>
     <row r="157" spans="1:10" ht="13" customHeight="1">
-      <c r="A157" s="97"/>
-      <c r="B157" s="81"/>
+      <c r="A157" s="100"/>
+      <c r="B157" s="94"/>
       <c r="C157" s="54">
         <v>28</v>
       </c>
-      <c r="D157" s="86" t="s">
+      <c r="D157" s="75" t="s">
         <v>232</v>
       </c>
-      <c r="E157" s="74"/>
-      <c r="F157" s="75"/>
+      <c r="E157" s="76"/>
+      <c r="F157" s="77"/>
       <c r="G157" s="48"/>
       <c r="H157" s="49">
         <f t="shared" si="3"/>
@@ -6193,16 +6203,16 @@
       <c r="J157" s="50"/>
     </row>
     <row r="158" spans="1:10" ht="13" customHeight="1">
-      <c r="A158" s="97"/>
-      <c r="B158" s="81"/>
+      <c r="A158" s="100"/>
+      <c r="B158" s="94"/>
       <c r="C158" s="54">
         <v>29</v>
       </c>
-      <c r="D158" s="86" t="s">
+      <c r="D158" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="E158" s="74"/>
-      <c r="F158" s="75"/>
+      <c r="E158" s="76"/>
+      <c r="F158" s="77"/>
       <c r="G158" s="48"/>
       <c r="H158" s="49">
         <f t="shared" si="3"/>
@@ -6212,16 +6222,16 @@
       <c r="J158" s="50"/>
     </row>
     <row r="159" spans="1:10" ht="13" customHeight="1">
-      <c r="A159" s="97"/>
-      <c r="B159" s="81"/>
+      <c r="A159" s="100"/>
+      <c r="B159" s="94"/>
       <c r="C159" s="54">
         <v>30</v>
       </c>
-      <c r="D159" s="86" t="s">
+      <c r="D159" s="75" t="s">
         <v>234</v>
       </c>
-      <c r="E159" s="74"/>
-      <c r="F159" s="75"/>
+      <c r="E159" s="76"/>
+      <c r="F159" s="77"/>
       <c r="G159" s="48"/>
       <c r="H159" s="49">
         <f t="shared" si="3"/>
@@ -6231,16 +6241,16 @@
       <c r="J159" s="50"/>
     </row>
     <row r="160" spans="1:10" ht="13" customHeight="1">
-      <c r="A160" s="97"/>
-      <c r="B160" s="82"/>
+      <c r="A160" s="100"/>
+      <c r="B160" s="95"/>
       <c r="C160" s="54">
         <v>31</v>
       </c>
-      <c r="D160" s="86" t="s">
+      <c r="D160" s="75" t="s">
         <v>235</v>
       </c>
-      <c r="E160" s="74"/>
-      <c r="F160" s="75"/>
+      <c r="E160" s="76"/>
+      <c r="F160" s="77"/>
       <c r="G160" s="48"/>
       <c r="H160" s="49">
         <f t="shared" si="3"/>
@@ -6250,32 +6260,32 @@
       <c r="J160" s="50"/>
     </row>
     <row r="161" spans="1:10" ht="22" customHeight="1">
-      <c r="A161" s="111" t="s">
+      <c r="A161" s="128" t="s">
         <v>236</v>
       </c>
-      <c r="B161" s="112"/>
-      <c r="C161" s="112"/>
-      <c r="D161" s="112"/>
-      <c r="E161" s="112"/>
-      <c r="F161" s="112"/>
-      <c r="G161" s="112"/>
-      <c r="H161" s="112"/>
-      <c r="I161" s="112"/>
-      <c r="J161" s="113"/>
+      <c r="B161" s="123"/>
+      <c r="C161" s="123"/>
+      <c r="D161" s="123"/>
+      <c r="E161" s="123"/>
+      <c r="F161" s="123"/>
+      <c r="G161" s="123"/>
+      <c r="H161" s="123"/>
+      <c r="I161" s="123"/>
+      <c r="J161" s="124"/>
     </row>
     <row r="162" spans="1:10" ht="14" customHeight="1">
       <c r="A162" s="69"/>
-      <c r="B162" s="83" t="s">
+      <c r="B162" s="153" t="s">
         <v>237</v>
       </c>
       <c r="C162" s="67">
         <v>1</v>
       </c>
-      <c r="D162" s="86" t="s">
+      <c r="D162" s="75" t="s">
         <v>238</v>
       </c>
-      <c r="E162" s="74"/>
-      <c r="F162" s="75"/>
+      <c r="E162" s="76"/>
+      <c r="F162" s="77"/>
       <c r="G162" s="48"/>
       <c r="H162" s="49">
         <f t="shared" ref="H162:H172" si="4">IF(G162="〇", 1, IF(G162="△", 0.5, 0))</f>
@@ -6288,15 +6298,15 @@
     </row>
     <row r="163" spans="1:10" ht="14" customHeight="1">
       <c r="A163" s="69"/>
-      <c r="B163" s="84"/>
+      <c r="B163" s="91"/>
       <c r="C163" s="67">
         <v>2</v>
       </c>
-      <c r="D163" s="86" t="s">
+      <c r="D163" s="75" t="s">
         <v>239</v>
       </c>
-      <c r="E163" s="74"/>
-      <c r="F163" s="75"/>
+      <c r="E163" s="76"/>
+      <c r="F163" s="77"/>
       <c r="G163" s="48"/>
       <c r="H163" s="49">
         <f t="shared" si="4"/>
@@ -6307,15 +6317,15 @@
     </row>
     <row r="164" spans="1:10" ht="14" customHeight="1">
       <c r="A164" s="69"/>
-      <c r="B164" s="84"/>
+      <c r="B164" s="91"/>
       <c r="C164" s="67">
         <v>3</v>
       </c>
-      <c r="D164" s="86" t="s">
+      <c r="D164" s="75" t="s">
         <v>240</v>
       </c>
-      <c r="E164" s="74"/>
-      <c r="F164" s="75"/>
+      <c r="E164" s="76"/>
+      <c r="F164" s="77"/>
       <c r="G164" s="48"/>
       <c r="H164" s="49">
         <f t="shared" si="4"/>
@@ -6330,15 +6340,15 @@
       <c r="A165" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="B165" s="84"/>
+      <c r="B165" s="91"/>
       <c r="C165" s="67">
         <v>4</v>
       </c>
-      <c r="D165" s="86" t="s">
+      <c r="D165" s="75" t="s">
         <v>241</v>
       </c>
-      <c r="E165" s="74"/>
-      <c r="F165" s="75"/>
+      <c r="E165" s="76"/>
+      <c r="F165" s="77"/>
       <c r="G165" s="48"/>
       <c r="H165" s="49">
         <f t="shared" si="4"/>
@@ -6349,15 +6359,15 @@
     </row>
     <row r="166" spans="1:10" ht="14" customHeight="1">
       <c r="A166" s="69"/>
-      <c r="B166" s="85"/>
+      <c r="B166" s="92"/>
       <c r="C166" s="67">
         <v>5</v>
       </c>
-      <c r="D166" s="86" t="s">
+      <c r="D166" s="75" t="s">
         <v>242</v>
       </c>
-      <c r="E166" s="74"/>
-      <c r="F166" s="75"/>
+      <c r="E166" s="76"/>
+      <c r="F166" s="77"/>
       <c r="G166" s="48"/>
       <c r="H166" s="49">
         <f t="shared" si="4"/>
@@ -6368,17 +6378,17 @@
     </row>
     <row r="167" spans="1:10" ht="14" customHeight="1">
       <c r="A167" s="69"/>
-      <c r="B167" s="101" t="s">
+      <c r="B167" s="151" t="s">
         <v>243</v>
       </c>
       <c r="C167" s="67">
         <v>6</v>
       </c>
-      <c r="D167" s="86" t="s">
+      <c r="D167" s="75" t="s">
         <v>244</v>
       </c>
-      <c r="E167" s="74"/>
-      <c r="F167" s="75"/>
+      <c r="E167" s="76"/>
+      <c r="F167" s="77"/>
       <c r="G167" s="48"/>
       <c r="H167" s="49">
         <f t="shared" si="4"/>
@@ -6389,15 +6399,15 @@
     </row>
     <row r="168" spans="1:10" ht="14" customHeight="1">
       <c r="A168" s="69"/>
-      <c r="B168" s="84"/>
+      <c r="B168" s="91"/>
       <c r="C168" s="67">
         <v>7</v>
       </c>
-      <c r="D168" s="86" t="s">
+      <c r="D168" s="75" t="s">
         <v>245</v>
       </c>
-      <c r="E168" s="74"/>
-      <c r="F168" s="75"/>
+      <c r="E168" s="76"/>
+      <c r="F168" s="77"/>
       <c r="G168" s="48"/>
       <c r="H168" s="49">
         <f t="shared" si="4"/>
@@ -6408,15 +6418,15 @@
     </row>
     <row r="169" spans="1:10" ht="14" customHeight="1">
       <c r="A169" s="69"/>
-      <c r="B169" s="84"/>
+      <c r="B169" s="91"/>
       <c r="C169" s="67">
         <v>8</v>
       </c>
-      <c r="D169" s="86" t="s">
+      <c r="D169" s="75" t="s">
         <v>246</v>
       </c>
-      <c r="E169" s="74"/>
-      <c r="F169" s="75"/>
+      <c r="E169" s="76"/>
+      <c r="F169" s="77"/>
       <c r="G169" s="48"/>
       <c r="H169" s="49">
         <f t="shared" si="4"/>
@@ -6427,15 +6437,15 @@
     </row>
     <row r="170" spans="1:10" ht="14" customHeight="1">
       <c r="A170" s="69"/>
-      <c r="B170" s="84"/>
+      <c r="B170" s="91"/>
       <c r="C170" s="67">
         <v>9</v>
       </c>
-      <c r="D170" s="86" t="s">
+      <c r="D170" s="75" t="s">
         <v>247</v>
       </c>
-      <c r="E170" s="74"/>
-      <c r="F170" s="75"/>
+      <c r="E170" s="76"/>
+      <c r="F170" s="77"/>
       <c r="G170" s="48"/>
       <c r="H170" s="49">
         <f t="shared" si="4"/>
@@ -6446,15 +6456,15 @@
     </row>
     <row r="171" spans="1:10" ht="14" customHeight="1">
       <c r="A171" s="69"/>
-      <c r="B171" s="84"/>
+      <c r="B171" s="91"/>
       <c r="C171" s="67">
         <v>10</v>
       </c>
-      <c r="D171" s="86" t="s">
+      <c r="D171" s="75" t="s">
         <v>248</v>
       </c>
-      <c r="E171" s="74"/>
-      <c r="F171" s="75"/>
+      <c r="E171" s="76"/>
+      <c r="F171" s="77"/>
       <c r="G171" s="48"/>
       <c r="H171" s="49">
         <f t="shared" si="4"/>
@@ -6465,15 +6475,15 @@
     </row>
     <row r="172" spans="1:10" ht="14" customHeight="1">
       <c r="A172" s="69"/>
-      <c r="B172" s="85"/>
+      <c r="B172" s="92"/>
       <c r="C172" s="67">
         <v>11</v>
       </c>
-      <c r="D172" s="86" t="s">
+      <c r="D172" s="75" t="s">
         <v>249</v>
       </c>
-      <c r="E172" s="74"/>
-      <c r="F172" s="75"/>
+      <c r="E172" s="76"/>
+      <c r="F172" s="77"/>
       <c r="G172" s="48"/>
       <c r="H172" s="49">
         <f t="shared" si="4"/>
@@ -6484,54 +6494,131 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="B105:B116"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="B135:B139"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="A83:A104"/>
-    <mergeCell ref="A105:A129"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A72:A81"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A130:A160"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="B153:B160"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="B83:B90"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="A161:J161"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F33:J33"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="B162:B166"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="B123:B125"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="A48:J49"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="B130:B134"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="B140:B152"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="B167:B172"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="D118:F118"/>
     <mergeCell ref="D135:F135"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="F40:G40"/>
@@ -6556,131 +6643,54 @@
     <mergeCell ref="D113:F113"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A17:D31"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="B130:B134"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B140:B152"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="A48:J49"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="A161:J161"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="B83:B90"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="F33:J33"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A130:A160"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="B167:B172"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B162:B166"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="B153:B160"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="B123:B125"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="A83:A104"/>
+    <mergeCell ref="A105:A129"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="A72:A81"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B105:B116"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="B135:B139"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D70:F70"/>
   </mergeCells>
   <phoneticPr fontId="30"/>
   <conditionalFormatting sqref="G72:G81 G83:G160 G162:G172">
